--- a/Slow Reveal Recreations/hull-house-nationalities/segments.xlsx
+++ b/Slow Reveal Recreations/hull-house-nationalities/segments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gvsu365-my.sharepoint.com/personal/s_cousilou_gvsu_edu/Documents/GVSU/Work/GA Position/Data Literacy/Visualization Recreations/Hull Houses/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="458" documentId="13_ncr:1_{278E54A3-B299-40B9-8BFE-17DE902D2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F335C5-ACA4-4237-B979-F66100272701}"/>
+  <xr:revisionPtr revIDLastSave="1184" documentId="13_ncr:1_{278E54A3-B299-40B9-8BFE-17DE902D2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E9B54AD-BEBC-4D9A-8BCB-CD51684C6565}"/>
   <bookViews>
-    <workbookView xWindow="33735" yWindow="0" windowWidth="9810" windowHeight="14745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="0" windowWidth="8535" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="segments" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="11">
   <si>
     <t>x1</t>
   </si>
@@ -121,10 +121,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -390,10 +386,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G361"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G558"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>3.79</v>
       </c>
@@ -439,7 +435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>6.9</v>
       </c>
@@ -462,7 +458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8.57</v>
       </c>
@@ -485,7 +481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>13.32</v>
       </c>
@@ -508,7 +504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3.79</v>
       </c>
@@ -531,7 +527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6.9</v>
       </c>
@@ -554,7 +550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8.57</v>
       </c>
@@ -577,7 +573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8.57</v>
       </c>
@@ -602,7 +598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8.57</v>
       </c>
@@ -627,7 +623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8.57</v>
       </c>
@@ -652,7 +648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9.67</v>
       </c>
@@ -676,7 +672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>A12+0.76</f>
         <v>10.43</v>
@@ -701,7 +697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>A13+2.04</f>
         <v>12.469999999999999</v>
@@ -726,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>A2+9.51+1</f>
         <v>14.3</v>
@@ -751,7 +747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14.3</v>
       </c>
@@ -775,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>A16+13.41</f>
         <v>27.71</v>
@@ -799,7 +795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>14.3</v>
       </c>
@@ -824,7 +820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>14.3</v>
       </c>
@@ -849,7 +845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>14.3</v>
       </c>
@@ -875,7 +871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>14.3</v>
       </c>
@@ -900,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14.3</v>
       </c>
@@ -925,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>14.3</v>
       </c>
@@ -950,7 +946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>14.3</v>
       </c>
@@ -975,7 +971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>14.3</v>
       </c>
@@ -1000,7 +996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>14.3</v>
       </c>
@@ -1025,7 +1021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>14.3</v>
       </c>
@@ -1050,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>16.899999999999999</v>
       </c>
@@ -1076,7 +1072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>16.899999999999999</v>
       </c>
@@ -1101,7 +1097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>A29+5.02</f>
         <v>21.919999999999998</v>
@@ -1127,7 +1123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>21.919999999999998</v>
       </c>
@@ -1152,7 +1148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>A15+0.98</f>
         <v>15.280000000000001</v>
@@ -1179,7 +1175,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>16.9-0.26</f>
         <v>16.639999999999997</v>
@@ -1204,7 +1200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>16.899999999999999</v>
       </c>
@@ -1227,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>A30</f>
         <v>21.919999999999998</v>
@@ -1253,7 +1249,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>21.919999999999998</v>
       </c>
@@ -1278,7 +1274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <f>27.71-1.53</f>
         <v>26.18</v>
@@ -1305,7 +1301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <f>26.18+0.26</f>
         <v>26.44</v>
@@ -1330,7 +1326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <f>27.71+1.13</f>
         <v>28.84</v>
@@ -1356,7 +1352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>28.84</v>
       </c>
@@ -1382,7 +1378,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <f>28.84+22.82</f>
         <v>51.66</v>
@@ -1408,7 +1404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>28.84</v>
       </c>
@@ -1432,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>49.38</v>
       </c>
@@ -1457,7 +1453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <f>28.84+0.7</f>
         <v>29.54</v>
@@ -1483,7 +1479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" ref="A45:A59" si="2">A44+0.7</f>
         <v>30.24</v>
@@ -1509,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="2"/>
         <v>30.939999999999998</v>
@@ -1535,7 +1531,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="2"/>
         <v>31.639999999999997</v>
@@ -1561,7 +1557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="2"/>
         <v>32.339999999999996</v>
@@ -1587,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="2"/>
         <v>33.04</v>
@@ -1613,7 +1609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="2"/>
         <v>33.74</v>
@@ -1639,7 +1635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="2"/>
         <v>34.440000000000005</v>
@@ -1665,7 +1661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="2"/>
         <v>35.140000000000008</v>
@@ -1691,7 +1687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="2"/>
         <v>35.840000000000011</v>
@@ -1717,7 +1713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="2"/>
         <v>36.540000000000013</v>
@@ -1743,7 +1739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="2"/>
         <v>37.240000000000016</v>
@@ -1769,7 +1765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="2"/>
         <v>37.940000000000019</v>
@@ -1795,7 +1791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="2"/>
         <v>38.640000000000022</v>
@@ -1821,7 +1817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="2"/>
         <v>39.340000000000025</v>
@@ -1847,7 +1843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="2"/>
         <v>40.040000000000028</v>
@@ -1873,7 +1869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <f>A59+1.07</f>
         <v>41.110000000000028</v>
@@ -1899,7 +1895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" ref="A61:A68" si="5">A60+1.07</f>
         <v>42.180000000000028</v>
@@ -1925,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="5"/>
         <v>43.250000000000028</v>
@@ -1951,7 +1947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="5"/>
         <v>44.320000000000029</v>
@@ -1977,7 +1973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="5"/>
         <v>45.390000000000029</v>
@@ -2003,7 +1999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="5"/>
         <v>46.460000000000029</v>
@@ -2029,7 +2025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="5"/>
         <v>47.53000000000003</v>
@@ -2055,7 +2051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="5"/>
         <v>48.60000000000003</v>
@@ -2081,7 +2077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" si="5"/>
         <v>49.67000000000003</v>
@@ -2107,7 +2103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <f>28.84+22.82</f>
         <v>51.66</v>
@@ -2133,7 +2129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <f>A69-2.28</f>
         <v>49.379999999999995</v>
@@ -2159,7 +2155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>27.71+1.13</f>
         <v>28.84</v>
@@ -2184,7 +2180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>28.84</v>
       </c>
@@ -2208,7 +2204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>28.84+22.8</f>
         <v>51.64</v>
@@ -2232,7 +2228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>28.84</v>
       </c>
@@ -2256,7 +2252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>28.84</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <f>28.84+4.06</f>
         <v>32.9</v>
@@ -2308,7 +2304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <f>28.84+4.06</f>
         <v>32.9</v>
@@ -2333,7 +2329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>35.58</v>
       </c>
@@ -2356,7 +2352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>36.5</v>
       </c>
@@ -2379,7 +2375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>36.5</v>
       </c>
@@ -2402,7 +2398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>37.840000000000003</v>
       </c>
@@ -2425,7 +2421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>37.840000000000003</v>
       </c>
@@ -2448,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>29.75</v>
       </c>
@@ -2471,7 +2467,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>29.75</v>
       </c>
@@ -2494,7 +2490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>31.04</v>
       </c>
@@ -2517,7 +2513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>31.04</v>
       </c>
@@ -2540,7 +2536,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>32.29</v>
       </c>
@@ -2563,7 +2559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>32.29</v>
       </c>
@@ -2586,7 +2582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>40.11</v>
       </c>
@@ -2609,7 +2605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>40.11</v>
       </c>
@@ -2632,7 +2628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>40.11</v>
       </c>
@@ -2655,7 +2651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>40.6</v>
       </c>
@@ -2678,7 +2674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>40.6</v>
       </c>
@@ -2701,7 +2697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>41.2</v>
       </c>
@@ -2724,7 +2720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>42.37</v>
       </c>
@@ -2747,7 +2743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>40.11</v>
       </c>
@@ -2771,7 +2767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>40.11</v>
       </c>
@@ -2795,7 +2791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>44.07</v>
       </c>
@@ -2818,7 +2814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>44.68</v>
       </c>
@@ -2841,7 +2837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>45.17</v>
       </c>
@@ -2864,7 +2860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>44.68</v>
       </c>
@@ -2887,7 +2883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>46.38</v>
       </c>
@@ -2910,7 +2906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>46.38</v>
       </c>
@@ -2933,7 +2929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>43.51</v>
       </c>
@@ -2956,7 +2952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>46.38</v>
       </c>
@@ -2979,7 +2975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>46.91</v>
       </c>
@@ -3002,7 +2998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>46.91</v>
       </c>
@@ -3025,7 +3021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>47.05</v>
       </c>
@@ -3048,7 +3044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>47.05</v>
       </c>
@@ -3071,7 +3067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>47.49</v>
       </c>
@@ -3094,7 +3090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>47.05</v>
       </c>
@@ -3117,7 +3113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>47.49</v>
       </c>
@@ -3140,7 +3136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>47.59</v>
       </c>
@@ -3163,7 +3159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>47.59</v>
       </c>
@@ -3186,7 +3182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>48.72</v>
       </c>
@@ -3209,7 +3205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>48.12</v>
       </c>
@@ -3232,7 +3228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>48.12</v>
       </c>
@@ -3255,7 +3251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>49.3</v>
       </c>
@@ -3278,7 +3274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>48.72</v>
       </c>
@@ -3301,7 +3297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>48.98</v>
       </c>
@@ -3324,7 +3320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>48.98</v>
       </c>
@@ -3347,7 +3343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>50.43</v>
       </c>
@@ -3370,7 +3366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>50.21</v>
       </c>
@@ -3393,7 +3389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>50.21</v>
       </c>
@@ -3416,7 +3412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>50.43</v>
       </c>
@@ -3439,7 +3435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>50.69</v>
       </c>
@@ -3462,7 +3458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>50.69</v>
       </c>
@@ -3485,7 +3481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>50.43</v>
       </c>
@@ -3508,7 +3504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>50.69</v>
       </c>
@@ -3531,7 +3527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>40.6</v>
       </c>
@@ -3554,7 +3550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>40.619999999999997</v>
       </c>
@@ -3577,7 +3573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>40.619999999999997</v>
       </c>
@@ -3600,7 +3596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>41.22</v>
       </c>
@@ -3623,7 +3619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>40.619999999999997</v>
       </c>
@@ -3646,7 +3642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>41.12</v>
       </c>
@@ -3669,7 +3665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>41.22</v>
       </c>
@@ -3692,7 +3688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>41.22</v>
       </c>
@@ -3715,7 +3711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>41.79</v>
       </c>
@@ -3738,7 +3734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>41.79</v>
       </c>
@@ -3761,7 +3757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>42.35</v>
       </c>
@@ -3784,7 +3780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>42.35</v>
       </c>
@@ -3807,7 +3803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>42.45</v>
       </c>
@@ -3830,7 +3826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>42.45</v>
       </c>
@@ -3853,7 +3849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>42.92</v>
       </c>
@@ -3876,7 +3872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>42.92</v>
       </c>
@@ -3899,7 +3895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>43.51</v>
       </c>
@@ -3922,7 +3918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>44.68</v>
       </c>
@@ -3945,7 +3941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>44.68</v>
       </c>
@@ -3968,7 +3964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>44.68</v>
       </c>
@@ -3991,7 +3987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>45.14</v>
       </c>
@@ -4014,7 +4010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>45.14</v>
       </c>
@@ -4037,7 +4033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>45.87</v>
       </c>
@@ -4060,7 +4056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>47.05</v>
       </c>
@@ -4083,7 +4079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>48.16</v>
       </c>
@@ -4106,7 +4102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>49.31</v>
       </c>
@@ -4129,7 +4125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>50.49</v>
       </c>
@@ -4152,7 +4148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>49.74</v>
       </c>
@@ -4175,7 +4171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>49.74</v>
       </c>
@@ -4199,7 +4195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>46.63</v>
       </c>
@@ -4222,7 +4218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>46.63</v>
       </c>
@@ -4245,7 +4241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>47.57</v>
       </c>
@@ -4268,7 +4264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>47.57</v>
       </c>
@@ -4291,7 +4287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>50.85</v>
       </c>
@@ -4314,7 +4310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>50.85</v>
       </c>
@@ -4337,7 +4333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>51.51</v>
       </c>
@@ -4360,7 +4356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>51.51</v>
       </c>
@@ -4383,7 +4379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>51.37</v>
       </c>
@@ -4406,7 +4402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>51.37</v>
       </c>
@@ -4429,7 +4425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>51.51</v>
       </c>
@@ -4452,7 +4448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>3.79</v>
       </c>
@@ -4475,7 +4471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>27.79</v>
       </c>
@@ -4498,7 +4494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>3.79</v>
       </c>
@@ -4521,7 +4517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>3.79</v>
       </c>
@@ -4544,7 +4540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>4.58</v>
       </c>
@@ -4568,7 +4564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>5.42</v>
       </c>
@@ -4592,7 +4588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>6.61</v>
       </c>
@@ -4616,7 +4612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>7.29</v>
       </c>
@@ -4640,7 +4636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>7.94</v>
       </c>
@@ -4664,7 +4660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>8.5399999999999991</v>
       </c>
@@ -4688,7 +4684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>9.16</v>
       </c>
@@ -4712,7 +4708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>9.74</v>
       </c>
@@ -4736,7 +4732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>10.3</v>
       </c>
@@ -4760,7 +4756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>10.77</v>
       </c>
@@ -4784,7 +4780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>11.07</v>
       </c>
@@ -4808,7 +4804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>11.59</v>
       </c>
@@ -4832,7 +4828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>12.09</v>
       </c>
@@ -4856,7 +4852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>12.24</v>
       </c>
@@ -4880,7 +4876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>12.73</v>
       </c>
@@ -4904,7 +4900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>13.39</v>
       </c>
@@ -4928,7 +4924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>13.9</v>
       </c>
@@ -4952,7 +4948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>14.08</v>
       </c>
@@ -4976,7 +4972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>14.08</v>
       </c>
@@ -4999,7 +4995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>14.64</v>
       </c>
@@ -5023,7 +5019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>14.8</v>
       </c>
@@ -5047,7 +5043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>14.8</v>
       </c>
@@ -5070,7 +5066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>15.31</v>
       </c>
@@ -5094,7 +5090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>15.94</v>
       </c>
@@ -5118,7 +5114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>16.440000000000001</v>
       </c>
@@ -5142,7 +5138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>16.97</v>
       </c>
@@ -5166,7 +5162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>15.94</v>
       </c>
@@ -5189,7 +5185,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>16.440000000000001</v>
       </c>
@@ -5212,7 +5208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>15.94</v>
       </c>
@@ -5235,7 +5231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>18.86</v>
       </c>
@@ -5259,7 +5255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>19.649999999999999</v>
       </c>
@@ -5283,7 +5279,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>20.329999999999998</v>
       </c>
@@ -5307,7 +5303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>18.86</v>
       </c>
@@ -5330,7 +5326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>20.91</v>
       </c>
@@ -5354,7 +5350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>21.14</v>
       </c>
@@ -5378,7 +5374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>21.42</v>
       </c>
@@ -5402,7 +5398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>21.97</v>
       </c>
@@ -5426,7 +5422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>22.5</v>
       </c>
@@ -5450,7 +5446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>20.91</v>
       </c>
@@ -5473,7 +5469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>23.14</v>
       </c>
@@ -5497,7 +5493,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>22.5</v>
       </c>
@@ -5520,7 +5516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>23.83</v>
       </c>
@@ -5544,7 +5540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>23.14</v>
       </c>
@@ -5567,7 +5563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>23.14</v>
       </c>
@@ -5590,7 +5586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>24.53</v>
       </c>
@@ -5614,7 +5610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>25.28</v>
       </c>
@@ -5638,7 +5634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>25.4</v>
       </c>
@@ -5662,7 +5658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>25.4</v>
       </c>
@@ -5685,7 +5681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>25.98</v>
       </c>
@@ -5709,7 +5705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>25.28</v>
       </c>
@@ -5732,7 +5728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>26.16</v>
       </c>
@@ -5756,7 +5752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>26.16</v>
       </c>
@@ -5779,7 +5775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>26.72</v>
       </c>
@@ -5803,7 +5799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>26.72</v>
       </c>
@@ -5826,7 +5822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>27.13</v>
       </c>
@@ -5850,7 +5846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>26.83</v>
       </c>
@@ -5874,7 +5870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>26.83</v>
       </c>
@@ -5897,7 +5893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>27.28</v>
       </c>
@@ -5921,7 +5917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>12.24</v>
       </c>
@@ -5945,7 +5941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>11.07</v>
       </c>
@@ -5969,7 +5965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>9.74</v>
       </c>
@@ -5993,7 +5989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>9.16</v>
       </c>
@@ -6017,7 +6013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>7.29</v>
       </c>
@@ -6041,7 +6037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>8.5399999999999991</v>
       </c>
@@ -6065,7 +6061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>7.29</v>
       </c>
@@ -6089,7 +6085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>5.42</v>
       </c>
@@ -6113,7 +6109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>5.42</v>
       </c>
@@ -6137,7 +6133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>3.79</v>
       </c>
@@ -6161,7 +6157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>3.79</v>
       </c>
@@ -6185,7 +6181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>3.79</v>
       </c>
@@ -6209,7 +6205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>3.79</v>
       </c>
@@ -6233,7 +6229,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>4.95</v>
       </c>
@@ -6256,7 +6252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>5.18</v>
       </c>
@@ -6279,7 +6275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>3.79</v>
       </c>
@@ -6302,7 +6298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>3.79</v>
       </c>
@@ -6325,7 +6321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>7.02</v>
       </c>
@@ -6348,7 +6344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>7.02</v>
       </c>
@@ -6371,7 +6367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>27.79</v>
       </c>
@@ -6394,7 +6390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>3.79</v>
       </c>
@@ -6417,7 +6413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>3.79</v>
       </c>
@@ -6440,7 +6436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>6.02</v>
       </c>
@@ -6463,7 +6459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>3.79</v>
       </c>
@@ -6486,7 +6482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>5.34</v>
       </c>
@@ -6509,7 +6505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>3.79</v>
       </c>
@@ -6532,7 +6528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>3.79</v>
       </c>
@@ -6555,7 +6551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>3.79</v>
       </c>
@@ -6578,7 +6574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>6.81</v>
       </c>
@@ -6601,7 +6597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>8.65</v>
       </c>
@@ -6624,7 +6620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>10.29</v>
       </c>
@@ -6648,7 +6644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>11.11</v>
       </c>
@@ -6672,7 +6668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>11.84</v>
       </c>
@@ -6696,7 +6692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>12.53</v>
       </c>
@@ -6719,7 +6715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>13.24</v>
       </c>
@@ -6743,7 +6739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>13.94</v>
       </c>
@@ -6767,7 +6763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>14.68</v>
       </c>
@@ -6791,7 +6787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>15.33</v>
       </c>
@@ -6815,7 +6811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>16.05</v>
       </c>
@@ -6839,7 +6835,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>16.850000000000001</v>
       </c>
@@ -6863,7 +6859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>18.350000000000001</v>
       </c>
@@ -6887,7 +6883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>19.350000000000001</v>
       </c>
@@ -6911,7 +6907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>19.350000000000001</v>
       </c>
@@ -6934,7 +6930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>19.690000000000001</v>
       </c>
@@ -6958,7 +6954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>21.16</v>
       </c>
@@ -6982,7 +6978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>22.54</v>
       </c>
@@ -7006,7 +7002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>23.87</v>
       </c>
@@ -7030,7 +7026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>25.31</v>
       </c>
@@ -7054,7 +7050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>26.75</v>
       </c>
@@ -7078,7 +7074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>28.84</v>
       </c>
@@ -7101,7 +7097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>28.84</v>
       </c>
@@ -7124,7 +7120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>51.64</v>
       </c>
@@ -7147,7 +7143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>28.84</v>
       </c>
@@ -7170,7 +7166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>29.18</v>
       </c>
@@ -7193,7 +7189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>29.6</v>
       </c>
@@ -7216,7 +7212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>30.33</v>
       </c>
@@ -7239,7 +7235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>31.73</v>
       </c>
@@ -7262,7 +7258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>31.73</v>
       </c>
@@ -7285,7 +7281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>32.43</v>
       </c>
@@ -7308,7 +7304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>33.14</v>
       </c>
@@ -7331,7 +7327,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>33.840000000000003</v>
       </c>
@@ -7354,7 +7350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>34.53</v>
       </c>
@@ -7377,7 +7373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>35.270000000000003</v>
       </c>
@@ -7401,7 +7397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>35.97</v>
       </c>
@@ -7425,7 +7421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>36.1</v>
       </c>
@@ -7449,7 +7445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>36.69</v>
       </c>
@@ -7473,7 +7469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>36.69</v>
       </c>
@@ -7496,7 +7492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>36.94</v>
       </c>
@@ -7520,7 +7516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>36.94</v>
       </c>
@@ -7543,7 +7539,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>37.36</v>
       </c>
@@ -7567,7 +7563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>37.47</v>
       </c>
@@ -7591,7 +7587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>37.47</v>
       </c>
@@ -7614,7 +7610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>38.71</v>
       </c>
@@ -7638,7 +7634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>38.1</v>
       </c>
@@ -7662,7 +7658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>38.82</v>
       </c>
@@ -7686,7 +7682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>38.82</v>
       </c>
@@ -7709,7 +7705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>39.53</v>
       </c>
@@ -7733,7 +7729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>40.26</v>
       </c>
@@ -7757,7 +7753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>39.53</v>
       </c>
@@ -7780,7 +7776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>40.01</v>
       </c>
@@ -7803,7 +7799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>40.01</v>
       </c>
@@ -7826,7 +7822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>40.200000000000003</v>
       </c>
@@ -7849,7 +7845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>40.26</v>
       </c>
@@ -7872,7 +7868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>40.89</v>
       </c>
@@ -7895,7 +7891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>40.89</v>
       </c>
@@ -7918,7 +7914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>41.5</v>
       </c>
@@ -7941,7 +7937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>40.89</v>
       </c>
@@ -7964,7 +7960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>41.5</v>
       </c>
@@ -7987,7 +7983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>41.62</v>
       </c>
@@ -8010,7 +8006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>41.62</v>
       </c>
@@ -8033,7 +8029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>42.25</v>
       </c>
@@ -8056,7 +8052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>42.25</v>
       </c>
@@ -8079,7 +8075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>42.25</v>
       </c>
@@ -8102,7 +8098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>42.93</v>
       </c>
@@ -8125,7 +8121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>42.98</v>
       </c>
@@ -8148,7 +8144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>43.66</v>
       </c>
@@ -8171,7 +8167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>43.76</v>
       </c>
@@ -8194,7 +8190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>43.76</v>
       </c>
@@ -8217,7 +8213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>44.43</v>
       </c>
@@ -8240,7 +8236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>45.09</v>
       </c>
@@ -8263,7 +8259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>44.43</v>
       </c>
@@ -8286,7 +8282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>45.09</v>
       </c>
@@ -8309,7 +8305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>45.09</v>
       </c>
@@ -8332,7 +8328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>45.26</v>
       </c>
@@ -8355,7 +8351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>45.09</v>
       </c>
@@ -8378,7 +8374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>45.81</v>
       </c>
@@ -8401,7 +8397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>46.41</v>
       </c>
@@ -8424,7 +8420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>46.41</v>
       </c>
@@ -8447,7 +8443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>46.59</v>
       </c>
@@ -8470,7 +8466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>46.65</v>
       </c>
@@ -8493,7 +8489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>46.65</v>
       </c>
@@ -8516,7 +8512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>47.28</v>
       </c>
@@ -8539,7 +8535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>47.28</v>
       </c>
@@ -8562,7 +8558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>48.01</v>
       </c>
@@ -8585,7 +8581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>48.71</v>
       </c>
@@ -8608,7 +8604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>49.41</v>
       </c>
@@ -8631,7 +8627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>49.57</v>
       </c>
@@ -8654,7 +8650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>50.11</v>
       </c>
@@ -8677,7 +8673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>50.85</v>
       </c>
@@ -8700,7 +8696,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>28.84</v>
       </c>
@@ -8723,7 +8719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>28.84</v>
       </c>
@@ -8746,7 +8742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>28.84</v>
       </c>
@@ -8769,7 +8765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>51.64</v>
       </c>
@@ -8792,7 +8788,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>29.63</v>
       </c>
@@ -8815,7 +8811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>30.1</v>
       </c>
@@ -8838,7 +8834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>29.52</v>
       </c>
@@ -8861,7 +8857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>29.38</v>
       </c>
@@ -8884,7 +8880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>28.84</v>
       </c>
@@ -8907,18 +8903,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>28.84</v>
+        <v>31.77</v>
       </c>
       <c r="B360">
-        <v>24.09</v>
+        <v>24.65</v>
       </c>
       <c r="C360">
-        <v>30.1</v>
+        <v>31.77</v>
       </c>
       <c r="D360">
-        <v>24.09</v>
+        <v>21.93</v>
       </c>
       <c r="E360" t="s">
         <v>7</v>
@@ -8930,18 +8926,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>28.84</v>
+        <v>31.1</v>
       </c>
       <c r="B361">
-        <v>23.38</v>
+        <v>24.65</v>
       </c>
       <c r="C361">
-        <v>31.77</v>
+        <v>31.1</v>
       </c>
       <c r="D361">
-        <v>23.38</v>
+        <v>21.93</v>
       </c>
       <c r="E361" t="s">
         <v>7</v>
@@ -8951,6 +8947,4474 @@
       </c>
       <c r="G361" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>31.27</v>
+      </c>
+      <c r="B362">
+        <v>23.38</v>
+      </c>
+      <c r="C362">
+        <v>31.27</v>
+      </c>
+      <c r="D362">
+        <v>22.08</v>
+      </c>
+      <c r="E362" t="s">
+        <v>7</v>
+      </c>
+      <c r="F362">
+        <v>6.1</v>
+      </c>
+      <c r="G362" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>28.84</v>
+      </c>
+      <c r="B363">
+        <v>24.09</v>
+      </c>
+      <c r="C363">
+        <v>30.1</v>
+      </c>
+      <c r="D363">
+        <v>24.09</v>
+      </c>
+      <c r="E363" t="s">
+        <v>7</v>
+      </c>
+      <c r="F363">
+        <v>6.1</v>
+      </c>
+      <c r="G363" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>28.84</v>
+      </c>
+      <c r="B364">
+        <v>23.38</v>
+      </c>
+      <c r="C364">
+        <v>31.77</v>
+      </c>
+      <c r="D364">
+        <v>23.38</v>
+      </c>
+      <c r="E364" t="s">
+        <v>7</v>
+      </c>
+      <c r="F364">
+        <v>6.1</v>
+      </c>
+      <c r="G364" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>31.77</v>
+      </c>
+      <c r="B365">
+        <v>24.29</v>
+      </c>
+      <c r="C365">
+        <v>32.43</v>
+      </c>
+      <c r="D365">
+        <v>24.29</v>
+      </c>
+      <c r="E365" t="s">
+        <v>7</v>
+      </c>
+      <c r="F365">
+        <v>6.1</v>
+      </c>
+      <c r="G365" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>32.43</v>
+      </c>
+      <c r="B366">
+        <v>24.65</v>
+      </c>
+      <c r="C366">
+        <v>32.43</v>
+      </c>
+      <c r="D366">
+        <v>21.93</v>
+      </c>
+      <c r="E366" t="s">
+        <v>7</v>
+      </c>
+      <c r="F366">
+        <v>6.1</v>
+      </c>
+      <c r="G366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>32.43</v>
+      </c>
+      <c r="B367">
+        <v>23.44</v>
+      </c>
+      <c r="C367">
+        <v>33.75</v>
+      </c>
+      <c r="D367">
+        <v>23.44</v>
+      </c>
+      <c r="E367" t="s">
+        <v>7</v>
+      </c>
+      <c r="F367">
+        <v>6.1</v>
+      </c>
+      <c r="G367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>33.14</v>
+      </c>
+      <c r="B368">
+        <v>24.65</v>
+      </c>
+      <c r="C368">
+        <v>33.14</v>
+      </c>
+      <c r="D368">
+        <v>21.93</v>
+      </c>
+      <c r="E368" t="s">
+        <v>7</v>
+      </c>
+      <c r="F368">
+        <v>6.1</v>
+      </c>
+      <c r="G368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>33.86</v>
+      </c>
+      <c r="B369">
+        <v>24.65</v>
+      </c>
+      <c r="C369">
+        <v>33.86</v>
+      </c>
+      <c r="D369">
+        <v>21.93</v>
+      </c>
+      <c r="E369" t="s">
+        <v>7</v>
+      </c>
+      <c r="F369">
+        <v>6.1</v>
+      </c>
+      <c r="G369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="B370">
+        <v>24.65</v>
+      </c>
+      <c r="C370">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="D370">
+        <v>21.93</v>
+      </c>
+      <c r="E370" t="s">
+        <v>7</v>
+      </c>
+      <c r="F370">
+        <v>6.1</v>
+      </c>
+      <c r="G370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="B371">
+        <v>23.97</v>
+      </c>
+      <c r="C371">
+        <v>35.28</v>
+      </c>
+      <c r="D371">
+        <v>23.97</v>
+      </c>
+      <c r="E371" t="s">
+        <v>7</v>
+      </c>
+      <c r="F371">
+        <v>6.1</v>
+      </c>
+      <c r="G371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>35.28</v>
+      </c>
+      <c r="B372">
+        <v>24.65</v>
+      </c>
+      <c r="C372">
+        <v>35.28</v>
+      </c>
+      <c r="D372">
+        <v>21.93</v>
+      </c>
+      <c r="E372" t="s">
+        <v>7</v>
+      </c>
+      <c r="F372">
+        <v>6.1</v>
+      </c>
+      <c r="G372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>36</v>
+      </c>
+      <c r="B373">
+        <v>24.65</v>
+      </c>
+      <c r="C373">
+        <v>36</v>
+      </c>
+      <c r="D373">
+        <v>21.93</v>
+      </c>
+      <c r="E373" t="s">
+        <v>7</v>
+      </c>
+      <c r="F373">
+        <v>6.1</v>
+      </c>
+      <c r="G373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>36</v>
+      </c>
+      <c r="B374">
+        <v>23.57</v>
+      </c>
+      <c r="C374">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="D374">
+        <v>23.57</v>
+      </c>
+      <c r="E374" t="s">
+        <v>7</v>
+      </c>
+      <c r="F374">
+        <v>6.1</v>
+      </c>
+      <c r="G374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>36.72</v>
+      </c>
+      <c r="B375">
+        <v>24.65</v>
+      </c>
+      <c r="C375">
+        <f>A375</f>
+        <v>36.72</v>
+      </c>
+      <c r="D375">
+        <v>21.93</v>
+      </c>
+      <c r="E375" t="s">
+        <v>7</v>
+      </c>
+      <c r="F375">
+        <v>6.1</v>
+      </c>
+      <c r="G375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="B376">
+        <v>24.65</v>
+      </c>
+      <c r="C376">
+        <f>A376</f>
+        <v>37.450000000000003</v>
+      </c>
+      <c r="D376">
+        <v>21.93</v>
+      </c>
+      <c r="E376" t="s">
+        <v>7</v>
+      </c>
+      <c r="F376">
+        <v>6.1</v>
+      </c>
+      <c r="G376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="B377">
+        <v>24.65</v>
+      </c>
+      <c r="C377">
+        <f>A377</f>
+        <v>38.119999999999997</v>
+      </c>
+      <c r="D377">
+        <v>21.93</v>
+      </c>
+      <c r="E377" t="s">
+        <v>7</v>
+      </c>
+      <c r="F377">
+        <v>6.1</v>
+      </c>
+      <c r="G377" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>38.83</v>
+      </c>
+      <c r="B378">
+        <v>24.65</v>
+      </c>
+      <c r="C378">
+        <v>38.83</v>
+      </c>
+      <c r="D378">
+        <v>21.93</v>
+      </c>
+      <c r="E378" t="s">
+        <v>7</v>
+      </c>
+      <c r="F378">
+        <v>6.1</v>
+      </c>
+      <c r="G378" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>39.549999999999997</v>
+      </c>
+      <c r="B379">
+        <v>24.65</v>
+      </c>
+      <c r="C379">
+        <v>39.549999999999997</v>
+      </c>
+      <c r="D379">
+        <v>21.93</v>
+      </c>
+      <c r="E379" t="s">
+        <v>7</v>
+      </c>
+      <c r="F379">
+        <v>6.1</v>
+      </c>
+      <c r="G379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>38.83</v>
+      </c>
+      <c r="B380">
+        <v>24.37</v>
+      </c>
+      <c r="C380">
+        <v>39.549999999999997</v>
+      </c>
+      <c r="D380">
+        <v>24.37</v>
+      </c>
+      <c r="E380" t="s">
+        <v>7</v>
+      </c>
+      <c r="F380">
+        <v>6.1</v>
+      </c>
+      <c r="G380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>40.26</v>
+      </c>
+      <c r="B381">
+        <v>24.65</v>
+      </c>
+      <c r="C381">
+        <v>40.26</v>
+      </c>
+      <c r="D381">
+        <v>21.93</v>
+      </c>
+      <c r="E381" t="s">
+        <v>7</v>
+      </c>
+      <c r="F381">
+        <v>6.1</v>
+      </c>
+      <c r="G381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>39.549999999999997</v>
+      </c>
+      <c r="B382">
+        <v>23.32</v>
+      </c>
+      <c r="C382">
+        <v>40.26</v>
+      </c>
+      <c r="D382">
+        <v>23.32</v>
+      </c>
+      <c r="E382" t="s">
+        <v>7</v>
+      </c>
+      <c r="F382">
+        <v>6.1</v>
+      </c>
+      <c r="G382" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>40.97</v>
+      </c>
+      <c r="B383">
+        <v>24.65</v>
+      </c>
+      <c r="C383">
+        <v>40.97</v>
+      </c>
+      <c r="D383">
+        <v>21.93</v>
+      </c>
+      <c r="E383" t="s">
+        <v>7</v>
+      </c>
+      <c r="F383">
+        <v>6.1</v>
+      </c>
+      <c r="G383" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>40.26</v>
+      </c>
+      <c r="B384">
+        <v>23.52</v>
+      </c>
+      <c r="C384">
+        <v>40.97</v>
+      </c>
+      <c r="D384">
+        <v>23.52</v>
+      </c>
+      <c r="E384" t="s">
+        <v>7</v>
+      </c>
+      <c r="F384">
+        <v>6.1</v>
+      </c>
+      <c r="G384" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>40.26</v>
+      </c>
+      <c r="B385">
+        <v>22.17</v>
+      </c>
+      <c r="C385">
+        <v>40.97</v>
+      </c>
+      <c r="D385">
+        <v>22.17</v>
+      </c>
+      <c r="E385" t="s">
+        <v>7</v>
+      </c>
+      <c r="F385">
+        <v>6.1</v>
+      </c>
+      <c r="G385" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>41.67</v>
+      </c>
+      <c r="B386">
+        <v>24.65</v>
+      </c>
+      <c r="C386">
+        <v>41.67</v>
+      </c>
+      <c r="D386">
+        <v>21.93</v>
+      </c>
+      <c r="E386" t="s">
+        <v>7</v>
+      </c>
+      <c r="F386">
+        <v>6.1</v>
+      </c>
+      <c r="G386" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>40.26</v>
+      </c>
+      <c r="B387">
+        <v>23.74</v>
+      </c>
+      <c r="C387">
+        <v>41.67</v>
+      </c>
+      <c r="D387">
+        <v>23.74</v>
+      </c>
+      <c r="E387" t="s">
+        <v>7</v>
+      </c>
+      <c r="F387">
+        <v>6.1</v>
+      </c>
+      <c r="G387" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>42.37</v>
+      </c>
+      <c r="B388">
+        <v>24.65</v>
+      </c>
+      <c r="C388">
+        <v>42.37</v>
+      </c>
+      <c r="D388">
+        <v>21.93</v>
+      </c>
+      <c r="E388" t="s">
+        <v>7</v>
+      </c>
+      <c r="F388">
+        <v>6.1</v>
+      </c>
+      <c r="G388" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>41.67</v>
+      </c>
+      <c r="B389">
+        <v>23.54</v>
+      </c>
+      <c r="C389">
+        <v>43.7</v>
+      </c>
+      <c r="D389">
+        <v>23.54</v>
+      </c>
+      <c r="E389" t="s">
+        <v>7</v>
+      </c>
+      <c r="F389">
+        <v>6.1</v>
+      </c>
+      <c r="G389" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>43.7</v>
+      </c>
+      <c r="B390">
+        <v>24.65</v>
+      </c>
+      <c r="C390">
+        <v>43.7</v>
+      </c>
+      <c r="D390">
+        <v>21.93</v>
+      </c>
+      <c r="E390" t="s">
+        <v>7</v>
+      </c>
+      <c r="F390">
+        <v>6.1</v>
+      </c>
+      <c r="G390" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>44.48</v>
+      </c>
+      <c r="B391">
+        <v>24.65</v>
+      </c>
+      <c r="C391">
+        <v>44.48</v>
+      </c>
+      <c r="D391">
+        <v>21.93</v>
+      </c>
+      <c r="E391" t="s">
+        <v>7</v>
+      </c>
+      <c r="F391">
+        <v>6.1</v>
+      </c>
+      <c r="G391" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>45.17</v>
+      </c>
+      <c r="B392">
+        <v>24.65</v>
+      </c>
+      <c r="C392">
+        <v>45.17</v>
+      </c>
+      <c r="D392">
+        <v>21.93</v>
+      </c>
+      <c r="E392" t="s">
+        <v>7</v>
+      </c>
+      <c r="F392">
+        <v>6.1</v>
+      </c>
+      <c r="G392" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>45.75</v>
+      </c>
+      <c r="B393">
+        <v>24.65</v>
+      </c>
+      <c r="C393">
+        <v>45.75</v>
+      </c>
+      <c r="D393">
+        <v>21.93</v>
+      </c>
+      <c r="E393" t="s">
+        <v>7</v>
+      </c>
+      <c r="F393">
+        <v>6.1</v>
+      </c>
+      <c r="G393" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>45.75</v>
+      </c>
+      <c r="B394">
+        <v>23.87</v>
+      </c>
+      <c r="C394">
+        <v>46.61</v>
+      </c>
+      <c r="D394">
+        <v>23.87</v>
+      </c>
+      <c r="E394" t="s">
+        <v>7</v>
+      </c>
+      <c r="F394">
+        <v>6.1</v>
+      </c>
+      <c r="G394" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>45.86</v>
+      </c>
+      <c r="B395">
+        <v>24.65</v>
+      </c>
+      <c r="C395">
+        <v>45.86</v>
+      </c>
+      <c r="D395">
+        <v>21.93</v>
+      </c>
+      <c r="E395" t="s">
+        <v>7</v>
+      </c>
+      <c r="F395">
+        <v>6.1</v>
+      </c>
+      <c r="G395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>45.86</v>
+      </c>
+      <c r="B396">
+        <v>24.04</v>
+      </c>
+      <c r="C396">
+        <v>46.61</v>
+      </c>
+      <c r="D396">
+        <v>24.04</v>
+      </c>
+      <c r="E396" t="s">
+        <v>7</v>
+      </c>
+      <c r="F396">
+        <v>6.1</v>
+      </c>
+      <c r="G396" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>46.61</v>
+      </c>
+      <c r="B397">
+        <v>24.65</v>
+      </c>
+      <c r="C397">
+        <v>46.61</v>
+      </c>
+      <c r="D397">
+        <v>21.93</v>
+      </c>
+      <c r="E397" t="s">
+        <v>7</v>
+      </c>
+      <c r="F397">
+        <v>6.1</v>
+      </c>
+      <c r="G397" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>46.61</v>
+      </c>
+      <c r="B398">
+        <v>24.15</v>
+      </c>
+      <c r="C398">
+        <v>47</v>
+      </c>
+      <c r="D398">
+        <v>24.15</v>
+      </c>
+      <c r="E398" t="s">
+        <v>7</v>
+      </c>
+      <c r="F398">
+        <v>6.1</v>
+      </c>
+      <c r="G398" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>47</v>
+      </c>
+      <c r="B399">
+        <v>24.15</v>
+      </c>
+      <c r="C399">
+        <v>47</v>
+      </c>
+      <c r="D399">
+        <v>23.44</v>
+      </c>
+      <c r="E399" t="s">
+        <v>7</v>
+      </c>
+      <c r="F399">
+        <v>6.1</v>
+      </c>
+      <c r="G399" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>46.61</v>
+      </c>
+      <c r="B400">
+        <v>23.44</v>
+      </c>
+      <c r="C400">
+        <v>47.35</v>
+      </c>
+      <c r="D400">
+        <v>23.44</v>
+      </c>
+      <c r="E400" t="s">
+        <v>7</v>
+      </c>
+      <c r="F400">
+        <v>6.1</v>
+      </c>
+      <c r="G400" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>47.25</v>
+      </c>
+      <c r="B401">
+        <v>23.44</v>
+      </c>
+      <c r="C401">
+        <v>47.25</v>
+      </c>
+      <c r="D401">
+        <v>21.93</v>
+      </c>
+      <c r="E401" t="s">
+        <v>7</v>
+      </c>
+      <c r="F401">
+        <v>6.1</v>
+      </c>
+      <c r="G401" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>48.03</v>
+      </c>
+      <c r="B402">
+        <v>24.65</v>
+      </c>
+      <c r="C402">
+        <v>48.03</v>
+      </c>
+      <c r="D402">
+        <v>21.93</v>
+      </c>
+      <c r="E402" t="s">
+        <v>7</v>
+      </c>
+      <c r="F402">
+        <v>6.1</v>
+      </c>
+      <c r="G402" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>48.74</v>
+      </c>
+      <c r="B403">
+        <v>24.65</v>
+      </c>
+      <c r="C403">
+        <v>48.74</v>
+      </c>
+      <c r="D403">
+        <v>21.93</v>
+      </c>
+      <c r="E403" t="s">
+        <v>7</v>
+      </c>
+      <c r="F403">
+        <v>6.1</v>
+      </c>
+      <c r="G403" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>48.03</v>
+      </c>
+      <c r="B404">
+        <v>24.01</v>
+      </c>
+      <c r="C404">
+        <v>48.74</v>
+      </c>
+      <c r="D404">
+        <v>24.01</v>
+      </c>
+      <c r="E404" t="s">
+        <v>7</v>
+      </c>
+      <c r="F404">
+        <v>6.1</v>
+      </c>
+      <c r="G404" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>48.03</v>
+      </c>
+      <c r="B405">
+        <v>23.83</v>
+      </c>
+      <c r="C405">
+        <v>48.74</v>
+      </c>
+      <c r="D405">
+        <v>23.83</v>
+      </c>
+      <c r="E405" t="s">
+        <v>7</v>
+      </c>
+      <c r="F405">
+        <v>6.1</v>
+      </c>
+      <c r="G405" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>48.74</v>
+      </c>
+      <c r="B406">
+        <v>24.01</v>
+      </c>
+      <c r="C406">
+        <v>49.27</v>
+      </c>
+      <c r="D406">
+        <v>24.01</v>
+      </c>
+      <c r="E406" t="s">
+        <v>7</v>
+      </c>
+      <c r="F406">
+        <v>6.1</v>
+      </c>
+      <c r="G406" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>49.27</v>
+      </c>
+      <c r="B407">
+        <v>24.01</v>
+      </c>
+      <c r="C407">
+        <v>49.27</v>
+      </c>
+      <c r="D407">
+        <v>23.34</v>
+      </c>
+      <c r="E407" t="s">
+        <v>7</v>
+      </c>
+      <c r="F407">
+        <v>6.1</v>
+      </c>
+      <c r="G407" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>49.27</v>
+      </c>
+      <c r="B408">
+        <v>23.34</v>
+      </c>
+      <c r="C408">
+        <v>49.42</v>
+      </c>
+      <c r="D408">
+        <v>23.34</v>
+      </c>
+      <c r="E408" t="s">
+        <v>7</v>
+      </c>
+      <c r="F408">
+        <v>6.1</v>
+      </c>
+      <c r="G408" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>49.42</v>
+      </c>
+      <c r="B409">
+        <v>24.65</v>
+      </c>
+      <c r="C409">
+        <v>49.42</v>
+      </c>
+      <c r="D409">
+        <v>21.93</v>
+      </c>
+      <c r="E409" t="s">
+        <v>7</v>
+      </c>
+      <c r="F409">
+        <v>6.1</v>
+      </c>
+      <c r="G409" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>48.74</v>
+      </c>
+      <c r="B410">
+        <v>23.33</v>
+      </c>
+      <c r="C410">
+        <v>48.86</v>
+      </c>
+      <c r="D410">
+        <v>23.33</v>
+      </c>
+      <c r="E410" t="s">
+        <v>7</v>
+      </c>
+      <c r="F410">
+        <v>6.1</v>
+      </c>
+      <c r="G410" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>48.86</v>
+      </c>
+      <c r="B411">
+        <v>23.33</v>
+      </c>
+      <c r="C411">
+        <v>48.86</v>
+      </c>
+      <c r="D411">
+        <v>22.32</v>
+      </c>
+      <c r="E411" t="s">
+        <v>7</v>
+      </c>
+      <c r="F411">
+        <v>6.1</v>
+      </c>
+      <c r="G411" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>48.86</v>
+      </c>
+      <c r="B412">
+        <v>22.32</v>
+      </c>
+      <c r="C412">
+        <v>49.42</v>
+      </c>
+      <c r="D412">
+        <v>22.32</v>
+      </c>
+      <c r="E412" t="s">
+        <v>7</v>
+      </c>
+      <c r="F412">
+        <v>6.1</v>
+      </c>
+      <c r="G412" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>50.13</v>
+      </c>
+      <c r="B413">
+        <v>24.65</v>
+      </c>
+      <c r="C413">
+        <v>50.13</v>
+      </c>
+      <c r="D413">
+        <v>21.93</v>
+      </c>
+      <c r="E413" t="s">
+        <v>7</v>
+      </c>
+      <c r="F413">
+        <v>6.1</v>
+      </c>
+      <c r="G413" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>49.42</v>
+      </c>
+      <c r="B414">
+        <v>23.34</v>
+      </c>
+      <c r="C414">
+        <v>49.8</v>
+      </c>
+      <c r="D414">
+        <v>23.34</v>
+      </c>
+      <c r="E414" t="s">
+        <v>7</v>
+      </c>
+      <c r="F414">
+        <v>6.1</v>
+      </c>
+      <c r="G414" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>49.54</v>
+      </c>
+      <c r="B415">
+        <v>23.34</v>
+      </c>
+      <c r="C415">
+        <v>49.54</v>
+      </c>
+      <c r="D415">
+        <v>21.93</v>
+      </c>
+      <c r="E415" t="s">
+        <v>7</v>
+      </c>
+      <c r="F415">
+        <v>6.1</v>
+      </c>
+      <c r="G415" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>49.8</v>
+      </c>
+      <c r="B416">
+        <v>23.34</v>
+      </c>
+      <c r="C416">
+        <v>49.8</v>
+      </c>
+      <c r="D416">
+        <v>23.81</v>
+      </c>
+      <c r="E416" t="s">
+        <v>7</v>
+      </c>
+      <c r="F416">
+        <v>6.1</v>
+      </c>
+      <c r="G416" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>49.8</v>
+      </c>
+      <c r="B417">
+        <v>23.81</v>
+      </c>
+      <c r="C417">
+        <v>50.13</v>
+      </c>
+      <c r="D417">
+        <v>23.81</v>
+      </c>
+      <c r="E417" t="s">
+        <v>7</v>
+      </c>
+      <c r="F417">
+        <v>6.1</v>
+      </c>
+      <c r="G417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>50.89</v>
+      </c>
+      <c r="B418">
+        <v>24.65</v>
+      </c>
+      <c r="C418">
+        <v>50.89</v>
+      </c>
+      <c r="D418">
+        <v>21.93</v>
+      </c>
+      <c r="E418" t="s">
+        <v>7</v>
+      </c>
+      <c r="F418">
+        <v>6.1</v>
+      </c>
+      <c r="G418" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>50.13</v>
+      </c>
+      <c r="B419">
+        <v>24.36</v>
+      </c>
+      <c r="C419">
+        <v>50.89</v>
+      </c>
+      <c r="D419">
+        <v>24.36</v>
+      </c>
+      <c r="E419" t="s">
+        <v>7</v>
+      </c>
+      <c r="F419">
+        <v>6.1</v>
+      </c>
+      <c r="G419" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>50.7</v>
+      </c>
+      <c r="B420">
+        <v>23.84</v>
+      </c>
+      <c r="C420">
+        <v>50.89</v>
+      </c>
+      <c r="D420">
+        <v>23.84</v>
+      </c>
+      <c r="E420" t="s">
+        <v>7</v>
+      </c>
+      <c r="F420">
+        <v>6.1</v>
+      </c>
+      <c r="G420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>50.7</v>
+      </c>
+      <c r="B421">
+        <v>23.84</v>
+      </c>
+      <c r="C421">
+        <v>50.7</v>
+      </c>
+      <c r="D421">
+        <v>22.67</v>
+      </c>
+      <c r="E421" t="s">
+        <v>7</v>
+      </c>
+      <c r="F421">
+        <v>6.1</v>
+      </c>
+      <c r="G421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>50.7</v>
+      </c>
+      <c r="B422">
+        <v>22.67</v>
+      </c>
+      <c r="C422">
+        <v>50.89</v>
+      </c>
+      <c r="D422">
+        <v>22.67</v>
+      </c>
+      <c r="E422" t="s">
+        <v>7</v>
+      </c>
+      <c r="F422">
+        <v>6.1</v>
+      </c>
+      <c r="G422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>4.08</v>
+      </c>
+      <c r="B423">
+        <v>20.6</v>
+      </c>
+      <c r="C423">
+        <v>27.83</v>
+      </c>
+      <c r="D423">
+        <v>20.6</v>
+      </c>
+      <c r="E423" t="s">
+        <v>6</v>
+      </c>
+      <c r="F423">
+        <v>7</v>
+      </c>
+      <c r="G423" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>4.08</v>
+      </c>
+      <c r="B424">
+        <v>14.48</v>
+      </c>
+      <c r="C424">
+        <v>27.83</v>
+      </c>
+      <c r="D424">
+        <v>14.48</v>
+      </c>
+      <c r="E424" t="s">
+        <v>6</v>
+      </c>
+      <c r="F424">
+        <v>7</v>
+      </c>
+      <c r="G424" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>4.08</v>
+      </c>
+      <c r="B425">
+        <v>20.6</v>
+      </c>
+      <c r="C425">
+        <v>4.08</v>
+      </c>
+      <c r="D425">
+        <v>14.48</v>
+      </c>
+      <c r="E425" t="s">
+        <v>6</v>
+      </c>
+      <c r="F425">
+        <v>7</v>
+      </c>
+      <c r="G425" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>27.83</v>
+      </c>
+      <c r="B426">
+        <v>20.6</v>
+      </c>
+      <c r="C426">
+        <v>27.83</v>
+      </c>
+      <c r="D426">
+        <v>14.48</v>
+      </c>
+      <c r="E426" t="s">
+        <v>6</v>
+      </c>
+      <c r="F426">
+        <v>7</v>
+      </c>
+      <c r="G426" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>5.42</v>
+      </c>
+      <c r="B427">
+        <v>20.6</v>
+      </c>
+      <c r="C427">
+        <f>A427</f>
+        <v>5.42</v>
+      </c>
+      <c r="D427">
+        <v>14.48</v>
+      </c>
+      <c r="E427" t="s">
+        <v>7</v>
+      </c>
+      <c r="F427">
+        <v>7</v>
+      </c>
+      <c r="G427" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>7.03</v>
+      </c>
+      <c r="B428">
+        <v>20.6</v>
+      </c>
+      <c r="C428">
+        <f t="shared" ref="C428:C434" si="15">A428</f>
+        <v>7.03</v>
+      </c>
+      <c r="D428">
+        <v>14.48</v>
+      </c>
+      <c r="E428" t="s">
+        <v>7</v>
+      </c>
+      <c r="F428">
+        <v>7</v>
+      </c>
+      <c r="G428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="B429">
+        <v>20.6</v>
+      </c>
+      <c r="C429">
+        <f t="shared" si="15"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D429">
+        <v>14.48</v>
+      </c>
+      <c r="E429" t="s">
+        <v>7</v>
+      </c>
+      <c r="F429">
+        <v>7</v>
+      </c>
+      <c r="G429" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>10.37</v>
+      </c>
+      <c r="B430">
+        <v>20.6</v>
+      </c>
+      <c r="C430">
+        <f t="shared" si="15"/>
+        <v>10.37</v>
+      </c>
+      <c r="D430">
+        <v>14.48</v>
+      </c>
+      <c r="E430" t="s">
+        <v>7</v>
+      </c>
+      <c r="F430">
+        <v>7</v>
+      </c>
+      <c r="G430" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>11.95</v>
+      </c>
+      <c r="B431">
+        <v>20.6</v>
+      </c>
+      <c r="C431">
+        <f t="shared" si="15"/>
+        <v>11.95</v>
+      </c>
+      <c r="D431">
+        <v>14.48</v>
+      </c>
+      <c r="E431" t="s">
+        <v>7</v>
+      </c>
+      <c r="F431">
+        <v>7</v>
+      </c>
+      <c r="G431" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>13.63</v>
+      </c>
+      <c r="B432">
+        <v>20.6</v>
+      </c>
+      <c r="C432">
+        <f t="shared" si="15"/>
+        <v>13.63</v>
+      </c>
+      <c r="D432">
+        <v>14.48</v>
+      </c>
+      <c r="E432" t="s">
+        <v>7</v>
+      </c>
+      <c r="F432">
+        <v>7</v>
+      </c>
+      <c r="G432" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>15.3</v>
+      </c>
+      <c r="B433">
+        <v>20.6</v>
+      </c>
+      <c r="C433">
+        <f t="shared" si="15"/>
+        <v>15.3</v>
+      </c>
+      <c r="D433">
+        <v>14.48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>7</v>
+      </c>
+      <c r="F433">
+        <v>7</v>
+      </c>
+      <c r="G433" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>16.97</v>
+      </c>
+      <c r="B434">
+        <v>20.6</v>
+      </c>
+      <c r="C434">
+        <f t="shared" si="15"/>
+        <v>16.97</v>
+      </c>
+      <c r="D434">
+        <v>14.48</v>
+      </c>
+      <c r="E434" t="s">
+        <v>7</v>
+      </c>
+      <c r="F434">
+        <v>7</v>
+      </c>
+      <c r="G434" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>4.08</v>
+      </c>
+      <c r="B435">
+        <v>17.62</v>
+      </c>
+      <c r="C435">
+        <v>27.83</v>
+      </c>
+      <c r="D435">
+        <v>17.62</v>
+      </c>
+      <c r="E435" t="s">
+        <v>7</v>
+      </c>
+      <c r="F435">
+        <v>7</v>
+      </c>
+      <c r="G435" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>18.43</v>
+      </c>
+      <c r="B436">
+        <v>20.6</v>
+      </c>
+      <c r="C436">
+        <f>A436</f>
+        <v>18.43</v>
+      </c>
+      <c r="D436">
+        <v>17.62</v>
+      </c>
+      <c r="E436" t="s">
+        <v>7</v>
+      </c>
+      <c r="F436">
+        <v>7</v>
+      </c>
+      <c r="G436" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>19.72</v>
+      </c>
+      <c r="B437">
+        <v>20.6</v>
+      </c>
+      <c r="C437">
+        <f t="shared" ref="C437:C449" si="16">A437</f>
+        <v>19.72</v>
+      </c>
+      <c r="D437">
+        <v>17.62</v>
+      </c>
+      <c r="E437" t="s">
+        <v>7</v>
+      </c>
+      <c r="F437">
+        <v>7</v>
+      </c>
+      <c r="G437" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>21.21</v>
+      </c>
+      <c r="B438">
+        <v>20.6</v>
+      </c>
+      <c r="C438">
+        <f t="shared" si="16"/>
+        <v>21.21</v>
+      </c>
+      <c r="D438">
+        <v>17.62</v>
+      </c>
+      <c r="E438" t="s">
+        <v>7</v>
+      </c>
+      <c r="F438">
+        <v>7</v>
+      </c>
+      <c r="G438" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>22.58</v>
+      </c>
+      <c r="B439">
+        <v>20.6</v>
+      </c>
+      <c r="C439">
+        <f t="shared" si="16"/>
+        <v>22.58</v>
+      </c>
+      <c r="D439">
+        <v>17.62</v>
+      </c>
+      <c r="E439" t="s">
+        <v>7</v>
+      </c>
+      <c r="F439">
+        <v>7</v>
+      </c>
+      <c r="G439" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>23.89</v>
+      </c>
+      <c r="B440">
+        <v>20.6</v>
+      </c>
+      <c r="C440">
+        <f t="shared" si="16"/>
+        <v>23.89</v>
+      </c>
+      <c r="D440">
+        <v>17.62</v>
+      </c>
+      <c r="E440" t="s">
+        <v>7</v>
+      </c>
+      <c r="F440">
+        <v>7</v>
+      </c>
+      <c r="G440" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>25.39</v>
+      </c>
+      <c r="B441">
+        <v>20.6</v>
+      </c>
+      <c r="C441">
+        <f t="shared" si="16"/>
+        <v>25.39</v>
+      </c>
+      <c r="D441">
+        <v>17.62</v>
+      </c>
+      <c r="E441" t="s">
+        <v>7</v>
+      </c>
+      <c r="F441">
+        <v>7</v>
+      </c>
+      <c r="G441" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>26.79</v>
+      </c>
+      <c r="B442">
+        <v>20.6</v>
+      </c>
+      <c r="C442">
+        <f t="shared" si="16"/>
+        <v>26.79</v>
+      </c>
+      <c r="D442">
+        <v>17.62</v>
+      </c>
+      <c r="E442" t="s">
+        <v>7</v>
+      </c>
+      <c r="F442">
+        <v>7</v>
+      </c>
+      <c r="G442" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="B443">
+        <v>17.62</v>
+      </c>
+      <c r="C443">
+        <f t="shared" si="16"/>
+        <v>18.309999999999999</v>
+      </c>
+      <c r="D443">
+        <v>14.48</v>
+      </c>
+      <c r="E443" t="s">
+        <v>7</v>
+      </c>
+      <c r="F443">
+        <v>7</v>
+      </c>
+      <c r="G443" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>19.75</v>
+      </c>
+      <c r="B444">
+        <v>17.62</v>
+      </c>
+      <c r="C444">
+        <f t="shared" si="16"/>
+        <v>19.75</v>
+      </c>
+      <c r="D444">
+        <v>14.48</v>
+      </c>
+      <c r="E444" t="s">
+        <v>7</v>
+      </c>
+      <c r="F444">
+        <v>7</v>
+      </c>
+      <c r="G444" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>21.34</v>
+      </c>
+      <c r="B445">
+        <v>17.62</v>
+      </c>
+      <c r="C445">
+        <f t="shared" si="16"/>
+        <v>21.34</v>
+      </c>
+      <c r="D445">
+        <v>14.48</v>
+      </c>
+      <c r="E445" t="s">
+        <v>7</v>
+      </c>
+      <c r="F445">
+        <v>7</v>
+      </c>
+      <c r="G445" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>22.34</v>
+      </c>
+      <c r="B446">
+        <v>17.62</v>
+      </c>
+      <c r="C446">
+        <f t="shared" si="16"/>
+        <v>22.34</v>
+      </c>
+      <c r="D446">
+        <v>14.48</v>
+      </c>
+      <c r="E446" t="s">
+        <v>7</v>
+      </c>
+      <c r="F446">
+        <v>7</v>
+      </c>
+      <c r="G446" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>23.66</v>
+      </c>
+      <c r="B447">
+        <v>17.62</v>
+      </c>
+      <c r="C447">
+        <f t="shared" si="16"/>
+        <v>23.66</v>
+      </c>
+      <c r="D447">
+        <v>14.48</v>
+      </c>
+      <c r="E447" t="s">
+        <v>7</v>
+      </c>
+      <c r="F447">
+        <v>7</v>
+      </c>
+      <c r="G447" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>25.09</v>
+      </c>
+      <c r="B448">
+        <v>17.62</v>
+      </c>
+      <c r="C448">
+        <f t="shared" si="16"/>
+        <v>25.09</v>
+      </c>
+      <c r="D448">
+        <v>14.48</v>
+      </c>
+      <c r="E448" t="s">
+        <v>7</v>
+      </c>
+      <c r="F448">
+        <v>7</v>
+      </c>
+      <c r="G448" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>26.52</v>
+      </c>
+      <c r="B449">
+        <v>17.62</v>
+      </c>
+      <c r="C449">
+        <f t="shared" si="16"/>
+        <v>26.52</v>
+      </c>
+      <c r="D449">
+        <v>14.48</v>
+      </c>
+      <c r="E449" t="s">
+        <v>7</v>
+      </c>
+      <c r="F449">
+        <v>7</v>
+      </c>
+      <c r="G449" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>4.08</v>
+      </c>
+      <c r="B450">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="C450">
+        <v>5.09</v>
+      </c>
+      <c r="D450">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="E450" t="s">
+        <v>7</v>
+      </c>
+      <c r="F450">
+        <v>7</v>
+      </c>
+      <c r="G450" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>4.08</v>
+      </c>
+      <c r="B451">
+        <v>16.55</v>
+      </c>
+      <c r="C451">
+        <v>4.68</v>
+      </c>
+      <c r="D451">
+        <v>16.55</v>
+      </c>
+      <c r="E451" t="s">
+        <v>7</v>
+      </c>
+      <c r="F451">
+        <v>7</v>
+      </c>
+      <c r="G451" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>4.68</v>
+      </c>
+      <c r="B452">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="C452">
+        <v>4.68</v>
+      </c>
+      <c r="D452">
+        <v>16.55</v>
+      </c>
+      <c r="E452" t="s">
+        <v>7</v>
+      </c>
+      <c r="F452">
+        <v>7</v>
+      </c>
+      <c r="G452" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>4.68</v>
+      </c>
+      <c r="B453">
+        <v>16.97</v>
+      </c>
+      <c r="C453">
+        <v>5.09</v>
+      </c>
+      <c r="D453">
+        <v>16.97</v>
+      </c>
+      <c r="E453" t="s">
+        <v>7</v>
+      </c>
+      <c r="F453">
+        <v>7</v>
+      </c>
+      <c r="G453" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>4.08</v>
+      </c>
+      <c r="B454">
+        <v>15.99</v>
+      </c>
+      <c r="C454">
+        <v>4.7</v>
+      </c>
+      <c r="D454">
+        <v>15.99</v>
+      </c>
+      <c r="E454" t="s">
+        <v>7</v>
+      </c>
+      <c r="F454">
+        <v>7</v>
+      </c>
+      <c r="G454" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>4.7</v>
+      </c>
+      <c r="B455">
+        <v>15.99</v>
+      </c>
+      <c r="C455">
+        <v>4.7</v>
+      </c>
+      <c r="D455">
+        <v>15.11</v>
+      </c>
+      <c r="E455" t="s">
+        <v>7</v>
+      </c>
+      <c r="F455">
+        <v>7</v>
+      </c>
+      <c r="G455" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>4.08</v>
+      </c>
+      <c r="B456">
+        <v>15.11</v>
+      </c>
+      <c r="C456">
+        <v>6.64</v>
+      </c>
+      <c r="D456">
+        <v>15.11</v>
+      </c>
+      <c r="E456" t="s">
+        <v>7</v>
+      </c>
+      <c r="F456">
+        <v>7</v>
+      </c>
+      <c r="G456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>6.64</v>
+      </c>
+      <c r="B457">
+        <v>15.11</v>
+      </c>
+      <c r="C457">
+        <v>6.64</v>
+      </c>
+      <c r="D457">
+        <v>14.48</v>
+      </c>
+      <c r="E457" t="s">
+        <v>7</v>
+      </c>
+      <c r="F457">
+        <v>7</v>
+      </c>
+      <c r="G457" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>5.42</v>
+      </c>
+      <c r="B458">
+        <v>17.37</v>
+      </c>
+      <c r="C458">
+        <v>6.81</v>
+      </c>
+      <c r="D458">
+        <v>15.95</v>
+      </c>
+      <c r="E458" t="s">
+        <v>7</v>
+      </c>
+      <c r="F458">
+        <v>7</v>
+      </c>
+      <c r="G458" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>6.81</v>
+      </c>
+      <c r="B459">
+        <v>15.95</v>
+      </c>
+      <c r="C459">
+        <v>6.44</v>
+      </c>
+      <c r="D459">
+        <v>15.6</v>
+      </c>
+      <c r="E459" t="s">
+        <v>7</v>
+      </c>
+      <c r="F459">
+        <v>7</v>
+      </c>
+      <c r="G459" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>6.44</v>
+      </c>
+      <c r="B460">
+        <v>15.6</v>
+      </c>
+      <c r="C460">
+        <v>5.42</v>
+      </c>
+      <c r="D460">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E460" t="s">
+        <v>7</v>
+      </c>
+      <c r="F460">
+        <v>7</v>
+      </c>
+      <c r="G460" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>7.03</v>
+      </c>
+      <c r="B461">
+        <v>15.22</v>
+      </c>
+      <c r="C461">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D461">
+        <v>15.22</v>
+      </c>
+      <c r="E461" t="s">
+        <v>7</v>
+      </c>
+      <c r="F461">
+        <v>7</v>
+      </c>
+      <c r="G461" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B462">
+        <v>15.22</v>
+      </c>
+      <c r="C462">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D462">
+        <v>15.09</v>
+      </c>
+      <c r="E462" t="s">
+        <v>7</v>
+      </c>
+      <c r="F462">
+        <v>7</v>
+      </c>
+      <c r="G462" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B463">
+        <v>15.09</v>
+      </c>
+      <c r="C463">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D463">
+        <v>15.09</v>
+      </c>
+      <c r="E463" t="s">
+        <v>7</v>
+      </c>
+      <c r="F463">
+        <v>7</v>
+      </c>
+      <c r="G463" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B465">
+        <v>20.58</v>
+      </c>
+      <c r="C465">
+        <v>51.66</v>
+      </c>
+      <c r="D465">
+        <v>20.58</v>
+      </c>
+      <c r="E465" t="s">
+        <v>6</v>
+      </c>
+      <c r="F465">
+        <v>8</v>
+      </c>
+      <c r="G465" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B466">
+        <v>17.95</v>
+      </c>
+      <c r="C466">
+        <v>51.66</v>
+      </c>
+      <c r="D466">
+        <v>17.95</v>
+      </c>
+      <c r="E466" t="s">
+        <v>6</v>
+      </c>
+      <c r="F466">
+        <v>8</v>
+      </c>
+      <c r="G466" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B467">
+        <v>20.58</v>
+      </c>
+      <c r="C467">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="D467">
+        <v>17.95</v>
+      </c>
+      <c r="E467" t="s">
+        <v>6</v>
+      </c>
+      <c r="F467">
+        <v>8</v>
+      </c>
+      <c r="G467" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>51.66</v>
+      </c>
+      <c r="B468">
+        <v>20.58</v>
+      </c>
+      <c r="C468">
+        <v>51.66</v>
+      </c>
+      <c r="D468">
+        <v>17.95</v>
+      </c>
+      <c r="E468" t="s">
+        <v>6</v>
+      </c>
+      <c r="F468">
+        <v>8</v>
+      </c>
+      <c r="G468" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>29.65</v>
+      </c>
+      <c r="B469">
+        <v>20.58</v>
+      </c>
+      <c r="C469">
+        <f>A469</f>
+        <v>29.65</v>
+      </c>
+      <c r="D469">
+        <v>17.95</v>
+      </c>
+      <c r="E469" t="s">
+        <v>7</v>
+      </c>
+      <c r="F469">
+        <v>8</v>
+      </c>
+      <c r="G469" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>30.35</v>
+      </c>
+      <c r="B470">
+        <v>20.58</v>
+      </c>
+      <c r="C470">
+        <f>A470</f>
+        <v>30.35</v>
+      </c>
+      <c r="D470">
+        <v>17.95</v>
+      </c>
+      <c r="E470" t="s">
+        <v>7</v>
+      </c>
+      <c r="F470">
+        <v>8</v>
+      </c>
+      <c r="G470" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>31.1</v>
+      </c>
+      <c r="B471">
+        <v>20.58</v>
+      </c>
+      <c r="C471">
+        <f t="shared" ref="C471:C499" si="17">A471</f>
+        <v>31.1</v>
+      </c>
+      <c r="D471">
+        <v>17.95</v>
+      </c>
+      <c r="E471" t="s">
+        <v>7</v>
+      </c>
+      <c r="F471">
+        <v>8</v>
+      </c>
+      <c r="G471" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>31.79</v>
+      </c>
+      <c r="B472">
+        <v>20.58</v>
+      </c>
+      <c r="C472">
+        <f t="shared" si="17"/>
+        <v>31.79</v>
+      </c>
+      <c r="D472">
+        <v>17.95</v>
+      </c>
+      <c r="E472" t="s">
+        <v>7</v>
+      </c>
+      <c r="F472">
+        <v>8</v>
+      </c>
+      <c r="G472" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>32.44</v>
+      </c>
+      <c r="B473">
+        <v>20.58</v>
+      </c>
+      <c r="C473">
+        <f t="shared" si="17"/>
+        <v>32.44</v>
+      </c>
+      <c r="D473">
+        <v>17.95</v>
+      </c>
+      <c r="E473" t="s">
+        <v>7</v>
+      </c>
+      <c r="F473">
+        <v>8</v>
+      </c>
+      <c r="G473" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>33.159999999999997</v>
+      </c>
+      <c r="B474">
+        <v>20.58</v>
+      </c>
+      <c r="C474">
+        <f t="shared" si="17"/>
+        <v>33.159999999999997</v>
+      </c>
+      <c r="D474">
+        <v>17.95</v>
+      </c>
+      <c r="E474" t="s">
+        <v>7</v>
+      </c>
+      <c r="F474">
+        <v>8</v>
+      </c>
+      <c r="G474" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>33.83</v>
+      </c>
+      <c r="B475">
+        <v>20.58</v>
+      </c>
+      <c r="C475">
+        <f t="shared" si="17"/>
+        <v>33.83</v>
+      </c>
+      <c r="D475">
+        <v>17.95</v>
+      </c>
+      <c r="E475" t="s">
+        <v>7</v>
+      </c>
+      <c r="F475">
+        <v>8</v>
+      </c>
+      <c r="G475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>34.590000000000003</v>
+      </c>
+      <c r="B476">
+        <v>20.58</v>
+      </c>
+      <c r="C476">
+        <f t="shared" si="17"/>
+        <v>34.590000000000003</v>
+      </c>
+      <c r="D476">
+        <v>17.95</v>
+      </c>
+      <c r="E476" t="s">
+        <v>7</v>
+      </c>
+      <c r="F476">
+        <v>8</v>
+      </c>
+      <c r="G476" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="B477">
+        <v>20.58</v>
+      </c>
+      <c r="C477">
+        <f t="shared" si="17"/>
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D477">
+        <v>17.95</v>
+      </c>
+      <c r="E477" t="s">
+        <v>7</v>
+      </c>
+      <c r="F477">
+        <v>8</v>
+      </c>
+      <c r="G477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>36.03</v>
+      </c>
+      <c r="B478">
+        <v>20.58</v>
+      </c>
+      <c r="C478">
+        <f t="shared" si="17"/>
+        <v>36.03</v>
+      </c>
+      <c r="D478">
+        <v>17.95</v>
+      </c>
+      <c r="E478" t="s">
+        <v>7</v>
+      </c>
+      <c r="F478">
+        <v>8</v>
+      </c>
+      <c r="G478" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>36.729999999999997</v>
+      </c>
+      <c r="B479">
+        <v>20.58</v>
+      </c>
+      <c r="C479">
+        <f t="shared" si="17"/>
+        <v>36.729999999999997</v>
+      </c>
+      <c r="D479">
+        <v>17.95</v>
+      </c>
+      <c r="E479" t="s">
+        <v>7</v>
+      </c>
+      <c r="F479">
+        <v>8</v>
+      </c>
+      <c r="G479" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>37.49</v>
+      </c>
+      <c r="B480">
+        <v>20.58</v>
+      </c>
+      <c r="C480">
+        <f t="shared" si="17"/>
+        <v>37.49</v>
+      </c>
+      <c r="D480">
+        <v>17.95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>7</v>
+      </c>
+      <c r="F480">
+        <v>8</v>
+      </c>
+      <c r="G480" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>38.21</v>
+      </c>
+      <c r="B481">
+        <v>20.58</v>
+      </c>
+      <c r="C481">
+        <f t="shared" si="17"/>
+        <v>38.21</v>
+      </c>
+      <c r="D481">
+        <v>17.95</v>
+      </c>
+      <c r="E481" t="s">
+        <v>7</v>
+      </c>
+      <c r="F481">
+        <v>8</v>
+      </c>
+      <c r="G481" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>38.93</v>
+      </c>
+      <c r="B482">
+        <v>20.58</v>
+      </c>
+      <c r="C482">
+        <f t="shared" si="17"/>
+        <v>38.93</v>
+      </c>
+      <c r="D482">
+        <v>17.95</v>
+      </c>
+      <c r="E482" t="s">
+        <v>7</v>
+      </c>
+      <c r="F482">
+        <v>8</v>
+      </c>
+      <c r="G482" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>39.64</v>
+      </c>
+      <c r="B483">
+        <v>20.58</v>
+      </c>
+      <c r="C483">
+        <f t="shared" si="17"/>
+        <v>39.64</v>
+      </c>
+      <c r="D483">
+        <v>17.95</v>
+      </c>
+      <c r="E483" t="s">
+        <v>7</v>
+      </c>
+      <c r="F483">
+        <v>8</v>
+      </c>
+      <c r="G483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>40.28</v>
+      </c>
+      <c r="B484">
+        <v>20.58</v>
+      </c>
+      <c r="C484">
+        <f t="shared" si="17"/>
+        <v>40.28</v>
+      </c>
+      <c r="D484">
+        <v>17.95</v>
+      </c>
+      <c r="E484" t="s">
+        <v>7</v>
+      </c>
+      <c r="F484">
+        <v>8</v>
+      </c>
+      <c r="G484" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>41</v>
+      </c>
+      <c r="B485">
+        <v>20.58</v>
+      </c>
+      <c r="C485">
+        <f t="shared" si="17"/>
+        <v>41</v>
+      </c>
+      <c r="D485">
+        <v>17.95</v>
+      </c>
+      <c r="E485" t="s">
+        <v>7</v>
+      </c>
+      <c r="F485">
+        <v>8</v>
+      </c>
+      <c r="G485" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>41.71</v>
+      </c>
+      <c r="B486">
+        <v>20.58</v>
+      </c>
+      <c r="C486">
+        <f t="shared" si="17"/>
+        <v>41.71</v>
+      </c>
+      <c r="D486">
+        <v>17.95</v>
+      </c>
+      <c r="E486" t="s">
+        <v>7</v>
+      </c>
+      <c r="F486">
+        <v>8</v>
+      </c>
+      <c r="G486" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>42.39</v>
+      </c>
+      <c r="B487">
+        <v>20.58</v>
+      </c>
+      <c r="C487">
+        <f t="shared" si="17"/>
+        <v>42.39</v>
+      </c>
+      <c r="D487">
+        <v>17.95</v>
+      </c>
+      <c r="E487" t="s">
+        <v>7</v>
+      </c>
+      <c r="F487">
+        <v>8</v>
+      </c>
+      <c r="G487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>43.09</v>
+      </c>
+      <c r="B488">
+        <v>20.58</v>
+      </c>
+      <c r="C488">
+        <f t="shared" si="17"/>
+        <v>43.09</v>
+      </c>
+      <c r="D488">
+        <v>17.95</v>
+      </c>
+      <c r="E488" t="s">
+        <v>7</v>
+      </c>
+      <c r="F488">
+        <v>8</v>
+      </c>
+      <c r="G488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>43.76</v>
+      </c>
+      <c r="B489">
+        <v>20.58</v>
+      </c>
+      <c r="C489">
+        <f t="shared" si="17"/>
+        <v>43.76</v>
+      </c>
+      <c r="D489">
+        <v>17.95</v>
+      </c>
+      <c r="E489" t="s">
+        <v>7</v>
+      </c>
+      <c r="F489">
+        <v>8</v>
+      </c>
+      <c r="G489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>44.52</v>
+      </c>
+      <c r="B490">
+        <v>20.58</v>
+      </c>
+      <c r="C490">
+        <f t="shared" si="17"/>
+        <v>44.52</v>
+      </c>
+      <c r="D490">
+        <v>17.95</v>
+      </c>
+      <c r="E490" t="s">
+        <v>7</v>
+      </c>
+      <c r="F490">
+        <v>8</v>
+      </c>
+      <c r="G490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>45.21</v>
+      </c>
+      <c r="B491">
+        <v>20.58</v>
+      </c>
+      <c r="C491">
+        <f t="shared" si="17"/>
+        <v>45.21</v>
+      </c>
+      <c r="D491">
+        <v>17.95</v>
+      </c>
+      <c r="E491" t="s">
+        <v>7</v>
+      </c>
+      <c r="F491">
+        <v>8</v>
+      </c>
+      <c r="G491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>45.9</v>
+      </c>
+      <c r="B492">
+        <v>20.58</v>
+      </c>
+      <c r="C492">
+        <f t="shared" si="17"/>
+        <v>45.9</v>
+      </c>
+      <c r="D492">
+        <v>17.95</v>
+      </c>
+      <c r="E492" t="s">
+        <v>7</v>
+      </c>
+      <c r="F492">
+        <v>8</v>
+      </c>
+      <c r="G492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>46.63</v>
+      </c>
+      <c r="B493">
+        <v>20.58</v>
+      </c>
+      <c r="C493">
+        <f t="shared" si="17"/>
+        <v>46.63</v>
+      </c>
+      <c r="D493">
+        <v>17.95</v>
+      </c>
+      <c r="E493" t="s">
+        <v>7</v>
+      </c>
+      <c r="F493">
+        <v>8</v>
+      </c>
+      <c r="G493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>47.38</v>
+      </c>
+      <c r="B494">
+        <v>20.58</v>
+      </c>
+      <c r="C494">
+        <f t="shared" si="17"/>
+        <v>47.38</v>
+      </c>
+      <c r="D494">
+        <v>17.95</v>
+      </c>
+      <c r="E494" t="s">
+        <v>7</v>
+      </c>
+      <c r="F494">
+        <v>8</v>
+      </c>
+      <c r="G494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>48.11</v>
+      </c>
+      <c r="B495">
+        <v>20.58</v>
+      </c>
+      <c r="C495">
+        <f t="shared" si="17"/>
+        <v>48.11</v>
+      </c>
+      <c r="D495">
+        <v>17.95</v>
+      </c>
+      <c r="E495" t="s">
+        <v>7</v>
+      </c>
+      <c r="F495">
+        <v>8</v>
+      </c>
+      <c r="G495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>48.75</v>
+      </c>
+      <c r="B496">
+        <v>20.58</v>
+      </c>
+      <c r="C496">
+        <f t="shared" si="17"/>
+        <v>48.75</v>
+      </c>
+      <c r="D496">
+        <v>17.95</v>
+      </c>
+      <c r="E496" t="s">
+        <v>7</v>
+      </c>
+      <c r="F496">
+        <v>8</v>
+      </c>
+      <c r="G496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>49.43</v>
+      </c>
+      <c r="B497">
+        <v>20.58</v>
+      </c>
+      <c r="C497">
+        <f t="shared" si="17"/>
+        <v>49.43</v>
+      </c>
+      <c r="D497">
+        <v>17.95</v>
+      </c>
+      <c r="E497" t="s">
+        <v>7</v>
+      </c>
+      <c r="F497">
+        <v>8</v>
+      </c>
+      <c r="G497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>50.17</v>
+      </c>
+      <c r="B498">
+        <v>20.58</v>
+      </c>
+      <c r="C498">
+        <f t="shared" si="17"/>
+        <v>50.17</v>
+      </c>
+      <c r="D498">
+        <v>17.95</v>
+      </c>
+      <c r="E498" t="s">
+        <v>7</v>
+      </c>
+      <c r="F498">
+        <v>8</v>
+      </c>
+      <c r="G498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>50.9</v>
+      </c>
+      <c r="B499">
+        <v>20.58</v>
+      </c>
+      <c r="C499">
+        <f t="shared" si="17"/>
+        <v>50.9</v>
+      </c>
+      <c r="D499">
+        <v>17.95</v>
+      </c>
+      <c r="E499" t="s">
+        <v>7</v>
+      </c>
+      <c r="F499">
+        <v>8</v>
+      </c>
+      <c r="G499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B501">
+        <v>17.39</v>
+      </c>
+      <c r="C501">
+        <v>51.66</v>
+      </c>
+      <c r="D501">
+        <v>17.39</v>
+      </c>
+      <c r="E501" t="s">
+        <v>6</v>
+      </c>
+      <c r="F501">
+        <v>8.1</v>
+      </c>
+      <c r="G501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B502">
+        <v>14.48</v>
+      </c>
+      <c r="C502">
+        <v>51.66</v>
+      </c>
+      <c r="D502">
+        <v>14.48</v>
+      </c>
+      <c r="E502" t="s">
+        <v>6</v>
+      </c>
+      <c r="F502">
+        <v>8.1</v>
+      </c>
+      <c r="G502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B503">
+        <v>17.39</v>
+      </c>
+      <c r="C503">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="D503">
+        <v>14.48</v>
+      </c>
+      <c r="E503" t="s">
+        <v>6</v>
+      </c>
+      <c r="F503">
+        <v>8.1</v>
+      </c>
+      <c r="G503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>51.66</v>
+      </c>
+      <c r="B504">
+        <v>17.39</v>
+      </c>
+      <c r="C504">
+        <v>51.66</v>
+      </c>
+      <c r="D504">
+        <v>14.48</v>
+      </c>
+      <c r="E504" t="s">
+        <v>6</v>
+      </c>
+      <c r="F504">
+        <v>8.1</v>
+      </c>
+      <c r="G504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B505">
+        <v>16.510000000000002</v>
+      </c>
+      <c r="C505">
+        <v>32.11</v>
+      </c>
+      <c r="D505">
+        <v>16.13</v>
+      </c>
+      <c r="E505" t="s">
+        <v>7</v>
+      </c>
+      <c r="F505">
+        <v>8.1</v>
+      </c>
+      <c r="G505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>32.11</v>
+      </c>
+      <c r="B506">
+        <v>16.13</v>
+      </c>
+      <c r="C506">
+        <v>32.11</v>
+      </c>
+      <c r="D506">
+        <v>14.48</v>
+      </c>
+      <c r="E506" t="s">
+        <v>7</v>
+      </c>
+      <c r="F506">
+        <v>8.1</v>
+      </c>
+      <c r="G506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <f>27.71+1.13</f>
+        <v>28.84</v>
+      </c>
+      <c r="B507">
+        <v>14.68</v>
+      </c>
+      <c r="C507">
+        <v>49.37</v>
+      </c>
+      <c r="D507">
+        <v>14.68</v>
+      </c>
+      <c r="E507" t="s">
+        <v>7</v>
+      </c>
+      <c r="F507">
+        <v>8.1</v>
+      </c>
+      <c r="G507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>49.37</v>
+      </c>
+      <c r="B508">
+        <v>14.68</v>
+      </c>
+      <c r="C508">
+        <v>49.37</v>
+      </c>
+      <c r="D508">
+        <v>14.48</v>
+      </c>
+      <c r="E508" t="s">
+        <v>7</v>
+      </c>
+      <c r="F508">
+        <v>8.1</v>
+      </c>
+      <c r="G508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>30.37</v>
+      </c>
+      <c r="B509">
+        <v>14.48</v>
+      </c>
+      <c r="C509">
+        <f>A509</f>
+        <v>30.37</v>
+      </c>
+      <c r="D509">
+        <v>17.39</v>
+      </c>
+      <c r="E509" t="s">
+        <v>7</v>
+      </c>
+      <c r="F509">
+        <v>8.1</v>
+      </c>
+      <c r="G509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>31.8</v>
+      </c>
+      <c r="B510">
+        <v>14.48</v>
+      </c>
+      <c r="C510">
+        <f>A510</f>
+        <v>31.8</v>
+      </c>
+      <c r="D510">
+        <v>17.39</v>
+      </c>
+      <c r="E510" t="s">
+        <v>7</v>
+      </c>
+      <c r="F510">
+        <v>8.1</v>
+      </c>
+      <c r="G510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>32.47</v>
+      </c>
+      <c r="B511">
+        <v>14.48</v>
+      </c>
+      <c r="C511">
+        <f t="shared" ref="C511:C532" si="18">A511</f>
+        <v>32.47</v>
+      </c>
+      <c r="D511">
+        <v>17.39</v>
+      </c>
+      <c r="E511" t="s">
+        <v>7</v>
+      </c>
+      <c r="F511">
+        <v>8.1</v>
+      </c>
+      <c r="G511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>33.18</v>
+      </c>
+      <c r="B512">
+        <v>14.48</v>
+      </c>
+      <c r="C512">
+        <f t="shared" si="18"/>
+        <v>33.18</v>
+      </c>
+      <c r="D512">
+        <v>17.39</v>
+      </c>
+      <c r="E512" t="s">
+        <v>7</v>
+      </c>
+      <c r="F512">
+        <v>8.1</v>
+      </c>
+      <c r="G512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="B513">
+        <v>14.48</v>
+      </c>
+      <c r="C513">
+        <f t="shared" si="18"/>
+        <v>33.840000000000003</v>
+      </c>
+      <c r="D513">
+        <v>17.39</v>
+      </c>
+      <c r="E513" t="s">
+        <v>7</v>
+      </c>
+      <c r="F513">
+        <v>8.1</v>
+      </c>
+      <c r="G513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>34.61</v>
+      </c>
+      <c r="B514">
+        <v>14.48</v>
+      </c>
+      <c r="C514">
+        <f t="shared" si="18"/>
+        <v>34.61</v>
+      </c>
+      <c r="D514">
+        <v>17.39</v>
+      </c>
+      <c r="E514" t="s">
+        <v>7</v>
+      </c>
+      <c r="F514">
+        <v>8.1</v>
+      </c>
+      <c r="G514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>35.32</v>
+      </c>
+      <c r="B515">
+        <v>14.48</v>
+      </c>
+      <c r="C515">
+        <f t="shared" si="18"/>
+        <v>35.32</v>
+      </c>
+      <c r="D515">
+        <v>17.39</v>
+      </c>
+      <c r="E515" t="s">
+        <v>7</v>
+      </c>
+      <c r="F515">
+        <v>8.1</v>
+      </c>
+      <c r="G515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>36.01</v>
+      </c>
+      <c r="B516">
+        <v>14.48</v>
+      </c>
+      <c r="C516">
+        <f t="shared" si="18"/>
+        <v>36.01</v>
+      </c>
+      <c r="D516">
+        <v>17.39</v>
+      </c>
+      <c r="E516" t="s">
+        <v>7</v>
+      </c>
+      <c r="F516">
+        <v>8.1</v>
+      </c>
+      <c r="G516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>36.74</v>
+      </c>
+      <c r="B517">
+        <v>14.48</v>
+      </c>
+      <c r="C517">
+        <f t="shared" si="18"/>
+        <v>36.74</v>
+      </c>
+      <c r="D517">
+        <v>17.39</v>
+      </c>
+      <c r="E517" t="s">
+        <v>7</v>
+      </c>
+      <c r="F517">
+        <v>8.1</v>
+      </c>
+      <c r="G517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>37.5</v>
+      </c>
+      <c r="B518">
+        <v>14.48</v>
+      </c>
+      <c r="C518">
+        <f t="shared" si="18"/>
+        <v>37.5</v>
+      </c>
+      <c r="D518">
+        <v>17.39</v>
+      </c>
+      <c r="E518" t="s">
+        <v>7</v>
+      </c>
+      <c r="F518">
+        <v>8.1</v>
+      </c>
+      <c r="G518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>38.25</v>
+      </c>
+      <c r="B519">
+        <v>14.48</v>
+      </c>
+      <c r="C519">
+        <f t="shared" si="18"/>
+        <v>38.25</v>
+      </c>
+      <c r="D519">
+        <v>17.39</v>
+      </c>
+      <c r="E519" t="s">
+        <v>7</v>
+      </c>
+      <c r="F519">
+        <v>8.1</v>
+      </c>
+      <c r="G519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>38.909999999999997</v>
+      </c>
+      <c r="B520">
+        <v>14.48</v>
+      </c>
+      <c r="C520">
+        <f t="shared" si="18"/>
+        <v>38.909999999999997</v>
+      </c>
+      <c r="D520">
+        <v>17.39</v>
+      </c>
+      <c r="E520" t="s">
+        <v>7</v>
+      </c>
+      <c r="F520">
+        <v>8.1</v>
+      </c>
+      <c r="G520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>40.28</v>
+      </c>
+      <c r="B521">
+        <v>14.48</v>
+      </c>
+      <c r="C521">
+        <f t="shared" si="18"/>
+        <v>40.28</v>
+      </c>
+      <c r="D521">
+        <v>17.39</v>
+      </c>
+      <c r="E521" t="s">
+        <v>7</v>
+      </c>
+      <c r="F521">
+        <v>8.1</v>
+      </c>
+      <c r="G521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>41.7</v>
+      </c>
+      <c r="B522">
+        <v>14.48</v>
+      </c>
+      <c r="C522">
+        <f t="shared" si="18"/>
+        <v>41.7</v>
+      </c>
+      <c r="D522">
+        <v>17.39</v>
+      </c>
+      <c r="E522" t="s">
+        <v>7</v>
+      </c>
+      <c r="F522">
+        <v>8.1</v>
+      </c>
+      <c r="G522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>44.52</v>
+      </c>
+      <c r="B523">
+        <v>14.48</v>
+      </c>
+      <c r="C523">
+        <f t="shared" si="18"/>
+        <v>44.52</v>
+      </c>
+      <c r="D523">
+        <v>17.39</v>
+      </c>
+      <c r="E523" t="s">
+        <v>7</v>
+      </c>
+      <c r="F523">
+        <v>8.1</v>
+      </c>
+      <c r="G523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>45.22</v>
+      </c>
+      <c r="B524">
+        <v>14.48</v>
+      </c>
+      <c r="C524">
+        <f t="shared" si="18"/>
+        <v>45.22</v>
+      </c>
+      <c r="D524">
+        <v>17.39</v>
+      </c>
+      <c r="E524" t="s">
+        <v>7</v>
+      </c>
+      <c r="F524">
+        <v>8.1</v>
+      </c>
+      <c r="G524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>45.94</v>
+      </c>
+      <c r="B525">
+        <v>14.48</v>
+      </c>
+      <c r="C525">
+        <f t="shared" si="18"/>
+        <v>45.94</v>
+      </c>
+      <c r="D525">
+        <v>17.39</v>
+      </c>
+      <c r="E525" t="s">
+        <v>7</v>
+      </c>
+      <c r="F525">
+        <v>8.1</v>
+      </c>
+      <c r="G525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A526">
+        <v>46.68</v>
+      </c>
+      <c r="B526">
+        <v>14.48</v>
+      </c>
+      <c r="C526">
+        <f t="shared" si="18"/>
+        <v>46.68</v>
+      </c>
+      <c r="D526">
+        <v>17.39</v>
+      </c>
+      <c r="E526" t="s">
+        <v>7</v>
+      </c>
+      <c r="F526">
+        <v>8.1</v>
+      </c>
+      <c r="G526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>47.4</v>
+      </c>
+      <c r="B527">
+        <v>14.48</v>
+      </c>
+      <c r="C527">
+        <f t="shared" si="18"/>
+        <v>47.4</v>
+      </c>
+      <c r="D527">
+        <v>17.39</v>
+      </c>
+      <c r="E527" t="s">
+        <v>7</v>
+      </c>
+      <c r="F527">
+        <v>8.1</v>
+      </c>
+      <c r="G527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A528">
+        <v>48.11</v>
+      </c>
+      <c r="B528">
+        <v>14.48</v>
+      </c>
+      <c r="C528">
+        <f t="shared" si="18"/>
+        <v>48.11</v>
+      </c>
+      <c r="D528">
+        <v>17.39</v>
+      </c>
+      <c r="E528" t="s">
+        <v>7</v>
+      </c>
+      <c r="F528">
+        <v>8.1</v>
+      </c>
+      <c r="G528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A529">
+        <v>48.8</v>
+      </c>
+      <c r="B529">
+        <v>14.48</v>
+      </c>
+      <c r="C529">
+        <f t="shared" si="18"/>
+        <v>48.8</v>
+      </c>
+      <c r="D529">
+        <v>17.39</v>
+      </c>
+      <c r="E529" t="s">
+        <v>7</v>
+      </c>
+      <c r="F529">
+        <v>8.1</v>
+      </c>
+      <c r="G529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A530">
+        <v>49.49</v>
+      </c>
+      <c r="B530">
+        <v>14.48</v>
+      </c>
+      <c r="C530">
+        <f t="shared" si="18"/>
+        <v>49.49</v>
+      </c>
+      <c r="D530">
+        <v>17.39</v>
+      </c>
+      <c r="E530" t="s">
+        <v>7</v>
+      </c>
+      <c r="F530">
+        <v>8.1</v>
+      </c>
+      <c r="G530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A531">
+        <v>50.2</v>
+      </c>
+      <c r="B531">
+        <v>14.48</v>
+      </c>
+      <c r="C531">
+        <f t="shared" si="18"/>
+        <v>50.2</v>
+      </c>
+      <c r="D531">
+        <v>17.39</v>
+      </c>
+      <c r="E531" t="s">
+        <v>7</v>
+      </c>
+      <c r="F531">
+        <v>8.1</v>
+      </c>
+      <c r="G531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A532">
+        <v>50.96</v>
+      </c>
+      <c r="B532">
+        <v>14.48</v>
+      </c>
+      <c r="C532">
+        <f t="shared" si="18"/>
+        <v>50.96</v>
+      </c>
+      <c r="D532">
+        <v>17.39</v>
+      </c>
+      <c r="E532" t="s">
+        <v>7</v>
+      </c>
+      <c r="F532">
+        <v>8.1</v>
+      </c>
+      <c r="G532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>32.47</v>
+      </c>
+      <c r="B533">
+        <v>16.2</v>
+      </c>
+      <c r="C533">
+        <v>38.25</v>
+      </c>
+      <c r="D533">
+        <v>16.2</v>
+      </c>
+      <c r="E533" t="s">
+        <v>7</v>
+      </c>
+      <c r="F533">
+        <v>8.1</v>
+      </c>
+      <c r="G533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A534">
+        <v>32.75</v>
+      </c>
+      <c r="B534">
+        <v>20.03</v>
+      </c>
+      <c r="C534">
+        <v>45.9</v>
+      </c>
+      <c r="D534">
+        <v>20.03</v>
+      </c>
+      <c r="E534" t="s">
+        <v>7</v>
+      </c>
+      <c r="F534">
+        <v>8.1</v>
+      </c>
+      <c r="G534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>45.9</v>
+      </c>
+      <c r="B535">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="C535">
+        <v>49.27</v>
+      </c>
+      <c r="D535">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="E535" t="s">
+        <v>7</v>
+      </c>
+      <c r="F535">
+        <v>8.1</v>
+      </c>
+      <c r="G535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A536">
+        <v>49.27</v>
+      </c>
+      <c r="B536">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="C536">
+        <v>49.27</v>
+      </c>
+      <c r="D536">
+        <v>16.21</v>
+      </c>
+      <c r="E536" t="s">
+        <v>7</v>
+      </c>
+      <c r="F536">
+        <v>8.1</v>
+      </c>
+      <c r="G536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>47.76</v>
+      </c>
+      <c r="B537">
+        <v>16.21</v>
+      </c>
+      <c r="C537">
+        <v>49.27</v>
+      </c>
+      <c r="D537">
+        <v>16.21</v>
+      </c>
+      <c r="E537" t="s">
+        <v>7</v>
+      </c>
+      <c r="F537">
+        <v>8.1</v>
+      </c>
+      <c r="G537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>47.76</v>
+      </c>
+      <c r="B538">
+        <v>16.21</v>
+      </c>
+      <c r="C538">
+        <v>47.76</v>
+      </c>
+      <c r="D538">
+        <v>16.02</v>
+      </c>
+      <c r="E538" t="s">
+        <v>7</v>
+      </c>
+      <c r="F538">
+        <v>8.1</v>
+      </c>
+      <c r="G538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A539">
+        <v>38.53</v>
+      </c>
+      <c r="B539">
+        <v>16.02</v>
+      </c>
+      <c r="C539">
+        <v>47.76</v>
+      </c>
+      <c r="D539">
+        <v>16.02</v>
+      </c>
+      <c r="E539" t="s">
+        <v>7</v>
+      </c>
+      <c r="F539">
+        <v>8.1</v>
+      </c>
+      <c r="G539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A540">
+        <v>38.53</v>
+      </c>
+      <c r="B540">
+        <v>16.73</v>
+      </c>
+      <c r="C540">
+        <v>38.53</v>
+      </c>
+      <c r="D540">
+        <v>14.48</v>
+      </c>
+      <c r="E540" t="s">
+        <v>7</v>
+      </c>
+      <c r="F540">
+        <v>8.1</v>
+      </c>
+      <c r="G540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A541">
+        <v>32.770000000000003</v>
+      </c>
+      <c r="B541">
+        <v>16.73</v>
+      </c>
+      <c r="C541">
+        <v>38.53</v>
+      </c>
+      <c r="D541">
+        <v>16.73</v>
+      </c>
+      <c r="E541" t="s">
+        <v>7</v>
+      </c>
+      <c r="F541">
+        <v>8.1</v>
+      </c>
+      <c r="G541" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A542">
+        <v>32.770000000000003</v>
+      </c>
+      <c r="B542">
+        <v>16.73</v>
+      </c>
+      <c r="C542">
+        <v>32.770000000000003</v>
+      </c>
+      <c r="D542">
+        <v>20.03</v>
+      </c>
+      <c r="E542" t="s">
+        <v>7</v>
+      </c>
+      <c r="F542">
+        <v>8.1</v>
+      </c>
+      <c r="G542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A543">
+        <v>51.44</v>
+      </c>
+      <c r="B543">
+        <v>20.58</v>
+      </c>
+      <c r="C543">
+        <v>51.44</v>
+      </c>
+      <c r="D543">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="E543" t="s">
+        <v>7</v>
+      </c>
+      <c r="F543">
+        <v>8.1</v>
+      </c>
+      <c r="G543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A544">
+        <v>51.44</v>
+      </c>
+      <c r="B544">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="C544">
+        <v>51.34</v>
+      </c>
+      <c r="D544">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="E544" t="s">
+        <v>7</v>
+      </c>
+      <c r="F544">
+        <v>8.1</v>
+      </c>
+      <c r="G544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A545">
+        <v>51.34</v>
+      </c>
+      <c r="B545">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="C545">
+        <v>51.34</v>
+      </c>
+      <c r="D545">
+        <v>18.18</v>
+      </c>
+      <c r="E545" t="s">
+        <v>7</v>
+      </c>
+      <c r="F545">
+        <v>8.1</v>
+      </c>
+      <c r="G545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A546">
+        <v>51.34</v>
+      </c>
+      <c r="B546">
+        <v>18.18</v>
+      </c>
+      <c r="C546">
+        <v>51.46</v>
+      </c>
+      <c r="D546">
+        <v>18.18</v>
+      </c>
+      <c r="E546" t="s">
+        <v>7</v>
+      </c>
+      <c r="F546">
+        <v>8.1</v>
+      </c>
+      <c r="G546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A547">
+        <v>51.46</v>
+      </c>
+      <c r="B547">
+        <v>18.18</v>
+      </c>
+      <c r="C547">
+        <v>51.46</v>
+      </c>
+      <c r="D547">
+        <v>17.07</v>
+      </c>
+      <c r="E547" t="s">
+        <v>7</v>
+      </c>
+      <c r="F547">
+        <v>8.1</v>
+      </c>
+      <c r="G547" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A548">
+        <v>51.46</v>
+      </c>
+      <c r="B548">
+        <v>17.07</v>
+      </c>
+      <c r="C548">
+        <v>51.36</v>
+      </c>
+      <c r="D548">
+        <v>17.07</v>
+      </c>
+      <c r="E548" t="s">
+        <v>7</v>
+      </c>
+      <c r="F548">
+        <v>8.1</v>
+      </c>
+      <c r="G548" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A549">
+        <v>51.36</v>
+      </c>
+      <c r="B549">
+        <v>17.07</v>
+      </c>
+      <c r="C549">
+        <v>51.36</v>
+      </c>
+      <c r="D549">
+        <v>16.079999999999998</v>
+      </c>
+      <c r="E549" t="s">
+        <v>7</v>
+      </c>
+      <c r="F549">
+        <v>8.1</v>
+      </c>
+      <c r="G549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>51.36</v>
+      </c>
+      <c r="B550">
+        <v>16.079999999999998</v>
+      </c>
+      <c r="C550">
+        <v>51.5</v>
+      </c>
+      <c r="D550">
+        <v>16.079999999999998</v>
+      </c>
+      <c r="E550" t="s">
+        <v>7</v>
+      </c>
+      <c r="F550">
+        <v>8.1</v>
+      </c>
+      <c r="G550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>51.5</v>
+      </c>
+      <c r="B551">
+        <v>16.079999999999998</v>
+      </c>
+      <c r="C551">
+        <v>51.5</v>
+      </c>
+      <c r="D551">
+        <v>14.48</v>
+      </c>
+      <c r="E551" t="s">
+        <v>7</v>
+      </c>
+      <c r="F551">
+        <v>8.1</v>
+      </c>
+      <c r="G551" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E553" t="s">
+        <v>6</v>
+      </c>
+      <c r="F553">
+        <v>9</v>
+      </c>
+      <c r="G553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E554" t="s">
+        <v>6</v>
+      </c>
+      <c r="F554">
+        <v>9</v>
+      </c>
+      <c r="G554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E555" t="s">
+        <v>6</v>
+      </c>
+      <c r="F555">
+        <v>9</v>
+      </c>
+      <c r="G555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E556" t="s">
+        <v>6</v>
+      </c>
+      <c r="F556">
+        <v>9</v>
+      </c>
+      <c r="G556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E557" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E558" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
